--- a/docs/Excel de etiquetes_plats.xlsx
+++ b/docs/Excel de etiquetes_plats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sis.tec\Documents\factures\G\incr\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{F89B5E0D-EF5A-4EE5-B630-941F3CB16624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3F7227-2486-4CF1-8396-540D9038ED41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="9" xr2:uid="{F9EE33E7-CC76-4D17-9D92-A49EB32673A7}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" firstSheet="4" activeTab="9" xr2:uid="{F9EE33E7-CC76-4D17-9D92-A49EB32673A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,6 @@
     <sheet name="Recompte" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029" concurrentManualCount="20"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -50,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2173" uniqueCount="866">
   <si>
     <t>Plato</t>
   </si>
@@ -2797,6 +2796,33 @@
   <si>
     <t>Por cada plato estadounidense que tengas en la carta se sumara un 2% al valor de los de Comida Rapida</t>
   </si>
+  <si>
+    <t>Corn dog</t>
+  </si>
+  <si>
+    <t>Club sandwich</t>
+  </si>
+  <si>
+    <t>Philly cheesesteak</t>
+  </si>
+  <si>
+    <t>Apple pie</t>
+  </si>
+  <si>
+    <t>New York cheesecake</t>
+  </si>
+  <si>
+    <t>Clam chowder</t>
+  </si>
+  <si>
+    <t>Pulled pork sandwich</t>
+  </si>
+  <si>
+    <t>Chicken and waffles</t>
+  </si>
+  <si>
+    <t>Pecan pie</t>
+  </si>
 </sst>
 </file>
 
@@ -2839,7 +2865,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2861,6 +2887,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0000FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2903,7 +2935,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2932,11 +2964,21 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="975">
+  <dxfs count="731">
     <dxf>
       <fill>
         <patternFill>
@@ -3190,6 +3232,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0000FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="3" tint="0.499984740745262"/>
@@ -3442,16 +3494,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="3" tint="0.499984740745262"/>
@@ -3704,16 +3746,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="3" tint="0.499984740745262"/>
@@ -9762,2280 +9794,12 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD5A775"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC3C327"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDC6B48"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD5A775"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC3C327"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDC6B48"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD5A775"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC3C327"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDC6B48"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD5A775"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC3C327"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDC6B48"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD5A775"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC3C327"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDC6B48"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD5A775"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC3C327"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDC6B48"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD5A775"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC3C327"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDC6B48"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD5A775"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC3C327"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDC6B48"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD5A775"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC3C327"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDC6B48"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -12058,6 +9822,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13057,7 +10838,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="M6:M9">
-    <cfRule type="duplicateValues" dxfId="947" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="730" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -13069,16 +10850,17 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{743FA71A-CF2A-481E-9F2B-47CF02847293}">
-  <dimension ref="C3:J181"/>
+  <dimension ref="C3:L192"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:10">
+    <row r="3" spans="4:12">
       <c r="D3" s="9" t="s">
         <v>0</v>
       </c>
@@ -13101,7 +10883,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="4" spans="4:10">
+    <row r="4" spans="4:12">
       <c r="D4" s="10" t="s">
         <v>53</v>
       </c>
@@ -13123,8 +10905,11 @@
       <c r="J4" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="5" spans="4:10">
+      <c r="L4" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="4:12">
       <c r="D5" s="10" t="s">
         <v>719</v>
       </c>
@@ -13146,8 +10931,11 @@
       <c r="J5" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="6" spans="4:10">
+      <c r="L5" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="4:12">
       <c r="D6" s="10" t="s">
         <v>60</v>
       </c>
@@ -13169,8 +10957,11 @@
       <c r="J6" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="7" spans="4:10">
+      <c r="L6" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="4:12">
       <c r="D7" s="10" t="s">
         <v>57</v>
       </c>
@@ -13192,8 +10983,11 @@
       <c r="J7" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="8" spans="4:10">
+      <c r="L7" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="4:12">
       <c r="D8" s="10" t="s">
         <v>736</v>
       </c>
@@ -13215,8 +11009,11 @@
       <c r="J8" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="9" spans="4:10">
+      <c r="L8" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="4:12">
       <c r="D9" s="10" t="s">
         <v>735</v>
       </c>
@@ -13238,8 +11035,11 @@
       <c r="J9" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="10" spans="4:10" ht="30">
+      <c r="L9" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="4:12" ht="30">
       <c r="D10" s="10" t="s">
         <v>737</v>
       </c>
@@ -13261,8 +11061,11 @@
       <c r="J10" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="11" spans="4:10">
+      <c r="L10" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="4:12">
       <c r="D11" s="10" t="s">
         <v>52</v>
       </c>
@@ -13284,8 +11087,11 @@
       <c r="J11" s="6" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="12" spans="4:10" ht="30">
+      <c r="L11" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="4:12">
       <c r="D12" s="10" t="s">
         <v>740</v>
       </c>
@@ -13307,8 +11113,11 @@
       <c r="J12" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="13" spans="4:10">
+      <c r="L12" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="4:12">
       <c r="D13" s="10" t="s">
         <v>66</v>
       </c>
@@ -13330,8 +11139,11 @@
       <c r="J13" s="6" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="14" spans="4:10" ht="30">
+      <c r="L13" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="4:12" ht="30">
       <c r="D14" s="10" t="s">
         <v>37</v>
       </c>
@@ -13353,8 +11165,11 @@
       <c r="J14" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="15" spans="4:10" ht="30">
+      <c r="L14" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="4:12" ht="30">
       <c r="D15" s="10" t="s">
         <v>49</v>
       </c>
@@ -13376,8 +11191,11 @@
       <c r="J15" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="16" spans="4:10" ht="30">
+      <c r="L15" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="4:12" ht="30">
       <c r="D16" s="10" t="s">
         <v>738</v>
       </c>
@@ -13399,8 +11217,11 @@
       <c r="J16" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="17" spans="4:10" ht="30">
+      <c r="L16" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:12" ht="30">
       <c r="D17" s="10" t="s">
         <v>98</v>
       </c>
@@ -13422,8 +11243,11 @@
       <c r="J17" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="18" spans="4:10" ht="30">
+      <c r="L17" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="4:12" ht="30">
       <c r="D18" s="10" t="s">
         <v>34</v>
       </c>
@@ -13445,8 +11269,11 @@
       <c r="J18" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="19" spans="4:10" ht="30">
+      <c r="L18" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="4:12" ht="30">
       <c r="D19" s="10" t="s">
         <v>137</v>
       </c>
@@ -13468,8 +11295,11 @@
       <c r="J19" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="20" spans="4:10" ht="30">
+      <c r="L19" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="4:12" ht="30">
       <c r="D20" s="10" t="s">
         <v>125</v>
       </c>
@@ -13491,8 +11321,11 @@
       <c r="J20" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="21" spans="4:10" ht="30">
+      <c r="L20" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:12" ht="30">
       <c r="D21" s="10" t="s">
         <v>44</v>
       </c>
@@ -13512,10 +11345,13 @@
         <v>705</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="22" spans="4:10" ht="30">
+        <v>781</v>
+      </c>
+      <c r="L21" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="4:12" ht="30">
       <c r="D22" s="10" t="s">
         <v>93</v>
       </c>
@@ -13537,8 +11373,11 @@
       <c r="J22" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="23" spans="4:10" ht="30">
+      <c r="L22" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="4:12" ht="30">
       <c r="D23" s="10" t="s">
         <v>40</v>
       </c>
@@ -13560,8 +11399,11 @@
       <c r="J23" s="6" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="24" spans="4:10" ht="30">
+      <c r="L23" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="4:12" ht="30">
       <c r="D24" s="10" t="s">
         <v>158</v>
       </c>
@@ -13583,8 +11425,11 @@
       <c r="J24" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="25" spans="4:10" ht="30">
+      <c r="L24" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="4:12" ht="30">
       <c r="D25" s="10" t="s">
         <v>157</v>
       </c>
@@ -13606,8 +11451,11 @@
       <c r="J25" s="6" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="26" spans="4:10" ht="30">
+      <c r="L25" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="4:12" ht="30">
       <c r="D26" s="10" t="s">
         <v>159</v>
       </c>
@@ -13629,8 +11477,11 @@
       <c r="J26" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="27" spans="4:10" ht="30">
+      <c r="L26" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:12" ht="30">
       <c r="D27" s="10" t="s">
         <v>739</v>
       </c>
@@ -13652,8 +11503,11 @@
       <c r="J27" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="28" spans="4:10" ht="30">
+      <c r="L27" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="4:12">
       <c r="D28" s="10" t="s">
         <v>113</v>
       </c>
@@ -13675,8 +11529,11 @@
       <c r="J28" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="29" spans="4:10" ht="30">
+      <c r="L28" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="4:12" ht="30">
       <c r="D29" s="10" t="s">
         <v>61</v>
       </c>
@@ -13698,8 +11555,11 @@
       <c r="J29" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="30" spans="4:10">
+      <c r="L29" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="4:12">
       <c r="D30" s="10" t="s">
         <v>108</v>
       </c>
@@ -13721,8 +11581,11 @@
       <c r="J30" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="31" spans="4:10" ht="30">
+      <c r="L30" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="4:12" ht="30">
       <c r="D31" s="10" t="s">
         <v>35</v>
       </c>
@@ -13744,8 +11607,11 @@
       <c r="J31" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="32" spans="4:10" ht="30">
+      <c r="L31" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="4:12" ht="30">
       <c r="D32" s="10" t="s">
         <v>91</v>
       </c>
@@ -13767,8 +11633,11 @@
       <c r="J32" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="33" spans="4:10" ht="30">
+      <c r="L32" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="4:12" ht="30">
       <c r="D33" s="10" t="s">
         <v>854</v>
       </c>
@@ -13790,8 +11659,11 @@
       <c r="J33" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="34" spans="4:10" ht="30">
+      <c r="L33" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="4:12" ht="30">
       <c r="D34" s="10" t="s">
         <v>161</v>
       </c>
@@ -13813,8 +11685,11 @@
       <c r="J34" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="35" spans="4:10" ht="30">
+      <c r="L34" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:12" ht="30">
       <c r="D35" s="10" t="s">
         <v>782</v>
       </c>
@@ -13836,8 +11711,11 @@
       <c r="J35" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="36" spans="4:10" ht="30">
+      <c r="L35" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="4:12">
       <c r="D36" s="10" t="s">
         <v>263</v>
       </c>
@@ -13859,8 +11737,11 @@
       <c r="J36" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="37" spans="4:10">
+      <c r="L36" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="4:12">
       <c r="D37" s="10" t="s">
         <v>143</v>
       </c>
@@ -13882,8 +11763,11 @@
       <c r="J37" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="38" spans="4:10">
+      <c r="L37" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="4:12">
       <c r="D38" s="10" t="s">
         <v>89</v>
       </c>
@@ -13905,8 +11789,11 @@
       <c r="J38" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="39" spans="4:10" ht="30">
+      <c r="L38" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:12">
       <c r="D39" s="10" t="s">
         <v>100</v>
       </c>
@@ -13928,8 +11815,11 @@
       <c r="J39" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="40" spans="4:10" ht="30">
+      <c r="L39" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="4:12" ht="30">
       <c r="D40" s="10" t="s">
         <v>131</v>
       </c>
@@ -13951,8 +11841,11 @@
       <c r="J40" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="41" spans="4:10" ht="30">
+      <c r="L40" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:12" ht="30">
       <c r="D41" s="10" t="s">
         <v>232</v>
       </c>
@@ -13974,8 +11867,11 @@
       <c r="J41" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="42" spans="4:10">
+      <c r="L41" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="4:12">
       <c r="D42" s="10" t="s">
         <v>741</v>
       </c>
@@ -13997,8 +11893,11 @@
       <c r="J42" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="43" spans="4:10" ht="30">
+      <c r="L42" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:12" ht="30">
       <c r="D43" s="10" t="s">
         <v>135</v>
       </c>
@@ -14020,8 +11919,11 @@
       <c r="J43" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="44" spans="4:10">
+      <c r="L43" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="4:12">
       <c r="D44" s="10" t="s">
         <v>302</v>
       </c>
@@ -14043,8 +11945,11 @@
       <c r="J44" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="45" spans="4:10" ht="30">
+      <c r="L44" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:12">
       <c r="D45" s="10" t="s">
         <v>145</v>
       </c>
@@ -14066,8 +11971,11 @@
       <c r="J45" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="46" spans="4:10">
+      <c r="L45" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="4:12">
       <c r="D46" s="10" t="s">
         <v>80</v>
       </c>
@@ -14089,8 +11997,11 @@
       <c r="J46" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="47" spans="4:10" ht="30">
+      <c r="L46" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:12" ht="30">
       <c r="D47" s="10" t="s">
         <v>290</v>
       </c>
@@ -14112,8 +12023,11 @@
       <c r="J47" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="48" spans="4:10" ht="30">
+      <c r="L47" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:12" ht="30">
       <c r="D48" s="10" t="s">
         <v>292</v>
       </c>
@@ -14135,8 +12049,11 @@
       <c r="J48" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="49" spans="4:10">
+      <c r="L48" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="4:12">
       <c r="D49" s="10" t="s">
         <v>182</v>
       </c>
@@ -14158,8 +12075,11 @@
       <c r="J49" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="50" spans="4:10">
+      <c r="L49" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="4:12">
       <c r="D50" s="10" t="s">
         <v>260</v>
       </c>
@@ -14181,8 +12101,11 @@
       <c r="J50" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="51" spans="4:10" ht="30">
+      <c r="L50" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="4:12" ht="30">
       <c r="D51" s="10" t="s">
         <v>235</v>
       </c>
@@ -14204,8 +12127,11 @@
       <c r="J51" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="52" spans="4:10" ht="30">
+      <c r="L51" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:12" ht="30">
       <c r="D52" s="10" t="s">
         <v>106</v>
       </c>
@@ -14227,8 +12153,11 @@
       <c r="J52" s="6" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="53" spans="4:10" ht="30">
+      <c r="L52" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="4:12">
       <c r="D53" s="10" t="s">
         <v>97</v>
       </c>
@@ -14250,8 +12179,11 @@
       <c r="J53" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="54" spans="4:10">
+      <c r="L53" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="4:12">
       <c r="D54" s="10" t="s">
         <v>198</v>
       </c>
@@ -14273,8 +12205,11 @@
       <c r="J54" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="55" spans="4:10" ht="30">
+      <c r="L54" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="4:12" ht="30">
       <c r="D55" s="10" t="s">
         <v>132</v>
       </c>
@@ -14296,8 +12231,11 @@
       <c r="J55" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="56" spans="4:10" ht="30">
+      <c r="L55" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="4:12" ht="30">
       <c r="D56" s="10" t="s">
         <v>119</v>
       </c>
@@ -14319,8 +12257,11 @@
       <c r="J56" s="6" t="s">
         <v>855</v>
       </c>
-    </row>
-    <row r="57" spans="4:10" ht="30">
+      <c r="L56" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="4:12" ht="30">
       <c r="D57" s="10" t="s">
         <v>216</v>
       </c>
@@ -14342,8 +12283,11 @@
       <c r="J57" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="58" spans="4:10" ht="30">
+      <c r="L57" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="4:12" ht="30">
       <c r="D58" s="10" t="s">
         <v>742</v>
       </c>
@@ -14365,8 +12309,11 @@
       <c r="J58" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="59" spans="4:10" ht="30">
+      <c r="L58" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="4:12" ht="30">
       <c r="D59" s="10" t="s">
         <v>63</v>
       </c>
@@ -14388,8 +12335,11 @@
       <c r="J59" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="60" spans="4:10" ht="30">
+      <c r="L59" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="4:12" ht="30">
       <c r="D60" s="10" t="s">
         <v>54</v>
       </c>
@@ -14411,8 +12361,11 @@
       <c r="J60" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="61" spans="4:10" ht="30">
+      <c r="L60" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="4:12" ht="30">
       <c r="D61" s="10" t="s">
         <v>205</v>
       </c>
@@ -14434,8 +12387,11 @@
       <c r="J61" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="62" spans="4:10" ht="30">
+      <c r="L61" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="4:12" ht="30">
       <c r="D62" s="10" t="s">
         <v>169</v>
       </c>
@@ -14457,8 +12413,11 @@
       <c r="J62" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="63" spans="4:10" ht="30">
+      <c r="L62" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="4:12" ht="30">
       <c r="D63" s="10" t="s">
         <v>148</v>
       </c>
@@ -14480,8 +12439,11 @@
       <c r="J63" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="64" spans="4:10" ht="30">
+      <c r="L63" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="4:12" ht="30">
       <c r="D64" s="10" t="s">
         <v>743</v>
       </c>
@@ -14503,8 +12465,11 @@
       <c r="J64" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="65" spans="4:10" ht="30">
+      <c r="L64" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="4:12" ht="30">
       <c r="D65" s="10" t="s">
         <v>744</v>
       </c>
@@ -14526,8 +12491,11 @@
       <c r="J65" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="66" spans="4:10" ht="30">
+      <c r="L65" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="4:12">
       <c r="D66" s="10" t="s">
         <v>224</v>
       </c>
@@ -14549,8 +12517,11 @@
       <c r="J66" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="67" spans="4:10" ht="30">
+      <c r="L66" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="4:12" ht="30">
       <c r="D67" s="10" t="s">
         <v>226</v>
       </c>
@@ -14572,8 +12543,11 @@
       <c r="J67" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="68" spans="4:10">
+      <c r="L67" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="4:12">
       <c r="D68" s="10" t="s">
         <v>214</v>
       </c>
@@ -14595,8 +12569,11 @@
       <c r="J68" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="69" spans="4:10" ht="30">
+      <c r="L68" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="4:12">
       <c r="D69" s="10" t="s">
         <v>745</v>
       </c>
@@ -14618,8 +12595,11 @@
       <c r="J69" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="70" spans="4:10" ht="30">
+      <c r="L69" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="4:12" ht="30">
       <c r="D70" s="10" t="s">
         <v>746</v>
       </c>
@@ -14641,8 +12621,11 @@
       <c r="J70" s="6" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="71" spans="4:10" ht="30">
+      <c r="L70" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="4:12">
       <c r="D71" s="10" t="s">
         <v>747</v>
       </c>
@@ -14664,8 +12647,11 @@
       <c r="J71" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="72" spans="4:10" ht="30">
+      <c r="L71" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="4:12" ht="30">
       <c r="D72" s="10" t="s">
         <v>748</v>
       </c>
@@ -14687,8 +12673,11 @@
       <c r="J72" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="73" spans="4:10" ht="30">
+      <c r="L72" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="4:12" ht="30">
       <c r="D73" s="10" t="s">
         <v>749</v>
       </c>
@@ -14710,8 +12699,11 @@
       <c r="J73" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="74" spans="4:10" ht="30">
+      <c r="L73" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="4:12" ht="30">
       <c r="D74" s="10" t="s">
         <v>750</v>
       </c>
@@ -14733,8 +12725,11 @@
       <c r="J74" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="75" spans="4:10" ht="30">
+      <c r="L74" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="4:12" ht="30">
       <c r="D75" s="10" t="s">
         <v>751</v>
       </c>
@@ -14756,8 +12751,11 @@
       <c r="J75" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="76" spans="4:10" ht="30">
+      <c r="L75" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="4:12" ht="30">
       <c r="D76" s="10" t="s">
         <v>756</v>
       </c>
@@ -14779,8 +12777,11 @@
       <c r="J76" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="77" spans="4:10" ht="30">
+      <c r="L76" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="4:12" ht="30">
       <c r="D77" s="10" t="s">
         <v>752</v>
       </c>
@@ -14802,8 +12803,11 @@
       <c r="J77" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="78" spans="4:10" ht="30">
+      <c r="L77" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="4:12" ht="30">
       <c r="D78" s="10" t="s">
         <v>151</v>
       </c>
@@ -14825,8 +12829,11 @@
       <c r="J78" s="6" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="79" spans="4:10" ht="30">
+      <c r="L78" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="4:12" ht="30">
       <c r="D79" s="10" t="s">
         <v>41</v>
       </c>
@@ -14848,8 +12855,11 @@
       <c r="J79" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="80" spans="4:10" ht="30">
+      <c r="L79" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="4:12">
       <c r="D80" s="10" t="s">
         <v>753</v>
       </c>
@@ -14871,8 +12881,11 @@
       <c r="J80" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="81" spans="4:10" ht="30">
+      <c r="L80" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="4:12" ht="30">
       <c r="D81" s="10" t="s">
         <v>754</v>
       </c>
@@ -14894,8 +12907,11 @@
       <c r="J81" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="82" spans="4:10" ht="30">
+      <c r="L81" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="4:12" ht="30">
       <c r="D82" s="10" t="s">
         <v>755</v>
       </c>
@@ -14917,8 +12933,11 @@
       <c r="J82" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="83" spans="4:10" ht="30">
+      <c r="L82" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="4:12" ht="30">
       <c r="D83" s="10" t="s">
         <v>853</v>
       </c>
@@ -14940,8 +12959,11 @@
       <c r="J83" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="84" spans="4:10">
+      <c r="L83" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="4:12">
       <c r="D84" s="10" t="s">
         <v>757</v>
       </c>
@@ -14963,8 +12985,11 @@
       <c r="J84" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="85" spans="4:10" ht="30">
+      <c r="L84" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="4:12" ht="30">
       <c r="D85" s="10" t="s">
         <v>758</v>
       </c>
@@ -14986,8 +13011,11 @@
       <c r="J85" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="86" spans="4:10" ht="30">
+      <c r="L85" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="4:12">
       <c r="D86" s="10" t="s">
         <v>759</v>
       </c>
@@ -15009,8 +13037,11 @@
       <c r="J86" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="87" spans="4:10" ht="30">
+      <c r="L86" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="4:12" ht="30">
       <c r="D87" s="10" t="s">
         <v>784</v>
       </c>
@@ -15032,8 +13063,11 @@
       <c r="J87" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="88" spans="4:10" ht="30">
+      <c r="L87" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="4:12" ht="30">
       <c r="D88" s="10" t="s">
         <v>785</v>
       </c>
@@ -15055,8 +13089,11 @@
       <c r="J88" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="89" spans="4:10" ht="30">
+      <c r="L88" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="4:12" ht="30">
       <c r="D89" s="10" t="s">
         <v>56</v>
       </c>
@@ -15078,8 +13115,11 @@
       <c r="J89" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="90" spans="4:10" ht="30">
+      <c r="L89" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="4:12" ht="30">
       <c r="D90" s="10" t="s">
         <v>786</v>
       </c>
@@ -15101,8 +13141,11 @@
       <c r="J90" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="91" spans="4:10" ht="30">
+      <c r="L90" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="4:12" ht="30">
       <c r="D91" s="10" t="s">
         <v>221</v>
       </c>
@@ -15124,8 +13167,11 @@
       <c r="J91" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="92" spans="4:10" ht="30">
+      <c r="L91" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="4:12" ht="30">
       <c r="D92" s="10" t="s">
         <v>787</v>
       </c>
@@ -15147,8 +13193,11 @@
       <c r="J92" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="93" spans="4:10" ht="30">
+      <c r="L92" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="4:12" ht="30">
       <c r="D93" s="10" t="s">
         <v>788</v>
       </c>
@@ -15170,8 +13219,11 @@
       <c r="J93" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="94" spans="4:10" ht="30">
+      <c r="L93" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="4:12" ht="30">
       <c r="D94" s="10" t="s">
         <v>185</v>
       </c>
@@ -15193,8 +13245,11 @@
       <c r="J94" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="95" spans="4:10" ht="30">
+      <c r="L94" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="4:12" ht="30">
       <c r="D95" s="10" t="s">
         <v>178</v>
       </c>
@@ -15216,8 +13271,11 @@
       <c r="J95" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="96" spans="4:10" ht="30">
+      <c r="L95" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="4:12" ht="30">
       <c r="D96" s="10" t="s">
         <v>789</v>
       </c>
@@ -15239,8 +13297,11 @@
       <c r="J96" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="97" spans="4:10">
+      <c r="L96" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="4:12">
       <c r="D97" s="10" t="s">
         <v>790</v>
       </c>
@@ -15262,8 +13323,11 @@
       <c r="J97" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="98" spans="4:10" ht="30">
+      <c r="L97" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="4:12" ht="30">
       <c r="D98" s="10" t="s">
         <v>177</v>
       </c>
@@ -15285,8 +13349,11 @@
       <c r="J98" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="99" spans="4:10" ht="30">
+      <c r="L98" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="4:12" ht="30">
       <c r="D99" s="10" t="s">
         <v>129</v>
       </c>
@@ -15308,8 +13375,11 @@
       <c r="J99" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="100" spans="4:10">
+      <c r="L99" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="4:12">
       <c r="D100" s="10" t="s">
         <v>791</v>
       </c>
@@ -15331,8 +13401,11 @@
       <c r="J100" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="101" spans="4:10">
+      <c r="L100" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="4:12">
       <c r="D101" s="10" t="s">
         <v>225</v>
       </c>
@@ -15354,8 +13427,11 @@
       <c r="J101" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="102" spans="4:10" ht="30">
+      <c r="L101" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="4:12" ht="30">
       <c r="D102" s="10" t="s">
         <v>792</v>
       </c>
@@ -15377,8 +13453,11 @@
       <c r="J102" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="103" spans="4:10" ht="30">
+      <c r="L102" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="4:12" ht="30">
       <c r="D103" s="10" t="s">
         <v>793</v>
       </c>
@@ -15400,8 +13479,11 @@
       <c r="J103" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="104" spans="4:10" ht="30">
+      <c r="L103" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="4:12" ht="30">
       <c r="D104" s="10" t="s">
         <v>794</v>
       </c>
@@ -15423,8 +13505,11 @@
       <c r="J104" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="105" spans="4:10">
+      <c r="L104" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="4:12">
       <c r="D105" s="10" t="s">
         <v>795</v>
       </c>
@@ -15446,8 +13531,11 @@
       <c r="J105" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="106" spans="4:10" ht="30">
+      <c r="L105" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="4:12" ht="30">
       <c r="D106" s="10" t="s">
         <v>189</v>
       </c>
@@ -15469,8 +13557,11 @@
       <c r="J106" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="107" spans="4:10" ht="30">
+      <c r="L106" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="4:12" ht="30">
       <c r="D107" s="10" t="s">
         <v>796</v>
       </c>
@@ -15492,8 +13583,11 @@
       <c r="J107" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="108" spans="4:10">
+      <c r="L107" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="4:12">
       <c r="D108" s="10" t="s">
         <v>797</v>
       </c>
@@ -15515,8 +13609,11 @@
       <c r="J108" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="109" spans="4:10" ht="30">
+      <c r="L108" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="4:12" ht="30">
       <c r="D109" s="10" t="s">
         <v>798</v>
       </c>
@@ -15538,8 +13635,11 @@
       <c r="J109" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="110" spans="4:10" ht="30">
+      <c r="L109" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="4:12" ht="30">
       <c r="D110" s="10" t="s">
         <v>799</v>
       </c>
@@ -15561,8 +13661,11 @@
       <c r="J110" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="111" spans="4:10" ht="30">
+      <c r="L110" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="4:12" ht="30">
       <c r="D111" s="10" t="s">
         <v>800</v>
       </c>
@@ -15584,8 +13687,11 @@
       <c r="J111" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="112" spans="4:10">
+      <c r="L111" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="4:12">
       <c r="D112" s="10" t="s">
         <v>96</v>
       </c>
@@ -15607,8 +13713,11 @@
       <c r="J112" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="113" spans="4:10" ht="30">
+      <c r="L112" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="4:12" ht="30">
       <c r="D113" s="10" t="s">
         <v>801</v>
       </c>
@@ -15630,8 +13739,11 @@
       <c r="J113" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="114" spans="4:10" ht="30">
+      <c r="L113" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="4:12" ht="30">
       <c r="D114" s="10" t="s">
         <v>802</v>
       </c>
@@ -15653,8 +13765,11 @@
       <c r="J114" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="115" spans="4:10" ht="30">
+      <c r="L114" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="4:12" ht="30">
       <c r="D115" s="10" t="s">
         <v>803</v>
       </c>
@@ -15676,8 +13791,11 @@
       <c r="J115" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="116" spans="4:10" ht="30">
+      <c r="L115" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="4:12" ht="30">
       <c r="D116" s="10" t="s">
         <v>804</v>
       </c>
@@ -15699,8 +13817,11 @@
       <c r="J116" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="117" spans="4:10" ht="30">
+      <c r="L116" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="4:12" ht="30">
       <c r="D117" s="10" t="s">
         <v>805</v>
       </c>
@@ -15722,8 +13843,11 @@
       <c r="J117" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="118" spans="4:10" ht="30">
+      <c r="L117" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="4:12" ht="30">
       <c r="D118" s="10" t="s">
         <v>806</v>
       </c>
@@ -15745,8 +13869,11 @@
       <c r="J118" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="119" spans="4:10">
+      <c r="L118" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="4:12">
       <c r="D119" s="10" t="s">
         <v>807</v>
       </c>
@@ -15768,8 +13895,11 @@
       <c r="J119" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="120" spans="4:10" ht="30">
+      <c r="L119" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="4:12" ht="30">
       <c r="D120" s="10" t="s">
         <v>808</v>
       </c>
@@ -15791,8 +13921,11 @@
       <c r="J120" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="121" spans="4:10" ht="30">
+      <c r="L120" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="4:12" ht="30">
       <c r="D121" s="10" t="s">
         <v>809</v>
       </c>
@@ -15814,8 +13947,11 @@
       <c r="J121" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="122" spans="4:10" ht="30">
+      <c r="L121" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="4:12" ht="30">
       <c r="D122" s="10" t="s">
         <v>810</v>
       </c>
@@ -15837,8 +13973,11 @@
       <c r="J122" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="123" spans="4:10" ht="30">
+      <c r="L122" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="4:12" ht="30">
       <c r="D123" s="10" t="s">
         <v>811</v>
       </c>
@@ -15860,8 +13999,11 @@
       <c r="J123" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="124" spans="4:10" ht="30">
+      <c r="L123" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="4:12" ht="30">
       <c r="D124" s="10" t="s">
         <v>812</v>
       </c>
@@ -15883,8 +14025,11 @@
       <c r="J124" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="125" spans="4:10" ht="30">
+      <c r="L124" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="4:12" ht="30">
       <c r="D125" s="10" t="s">
         <v>813</v>
       </c>
@@ -15906,8 +14051,11 @@
       <c r="J125" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="126" spans="4:10" ht="30">
+      <c r="L125" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="4:12" ht="30">
       <c r="D126" s="10" t="s">
         <v>179</v>
       </c>
@@ -15929,8 +14077,11 @@
       <c r="J126" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="127" spans="4:10" ht="30">
+      <c r="L126" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="4:12" ht="30">
       <c r="D127" s="10" t="s">
         <v>814</v>
       </c>
@@ -15952,8 +14103,11 @@
       <c r="J127" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="128" spans="4:10" ht="30">
+      <c r="L127" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="4:12" ht="30">
       <c r="D128" s="10" t="s">
         <v>74</v>
       </c>
@@ -15975,8 +14129,11 @@
       <c r="J128" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="129" spans="4:10" ht="30">
+      <c r="L128" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="4:12" ht="30">
       <c r="D129" s="10" t="s">
         <v>815</v>
       </c>
@@ -15998,8 +14155,11 @@
       <c r="J129" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="130" spans="4:10" ht="30">
+      <c r="L129" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="4:12" ht="30">
       <c r="D130" s="10" t="s">
         <v>71</v>
       </c>
@@ -16021,8 +14181,11 @@
       <c r="J130" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="131" spans="4:10" ht="30">
+      <c r="L130" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="4:12" ht="30">
       <c r="D131" s="10" t="s">
         <v>816</v>
       </c>
@@ -16044,8 +14207,11 @@
       <c r="J131" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="132" spans="4:10" ht="30">
+      <c r="L131" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="4:12" ht="30">
       <c r="D132" s="10" t="s">
         <v>817</v>
       </c>
@@ -16067,8 +14233,11 @@
       <c r="J132" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="133" spans="4:10" ht="30">
+      <c r="L132" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="4:12" ht="30">
       <c r="D133" s="10" t="s">
         <v>818</v>
       </c>
@@ -16090,8 +14259,11 @@
       <c r="J133" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="134" spans="4:10" ht="30">
+      <c r="L133" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="4:12" ht="30">
       <c r="D134" s="10" t="s">
         <v>819</v>
       </c>
@@ -16113,8 +14285,11 @@
       <c r="J134" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="135" spans="4:10">
+      <c r="L134" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="4:12">
       <c r="D135" s="10" t="s">
         <v>820</v>
       </c>
@@ -16136,8 +14311,11 @@
       <c r="J135" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="136" spans="4:10" ht="30">
+      <c r="L135" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="4:12" ht="30">
       <c r="D136" s="10" t="s">
         <v>821</v>
       </c>
@@ -16159,8 +14337,11 @@
       <c r="J136" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="137" spans="4:10" ht="30">
+      <c r="L136" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="4:12" ht="30">
       <c r="D137" s="10" t="s">
         <v>822</v>
       </c>
@@ -16182,8 +14363,11 @@
       <c r="J137" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="138" spans="4:10" ht="30">
+      <c r="L137" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="4:12" ht="30">
       <c r="D138" s="10" t="s">
         <v>231</v>
       </c>
@@ -16205,8 +14389,11 @@
       <c r="J138" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="139" spans="4:10">
+      <c r="L138" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="4:12">
       <c r="D139" s="10" t="s">
         <v>228</v>
       </c>
@@ -16228,8 +14415,11 @@
       <c r="J139" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="140" spans="4:10" ht="30">
+      <c r="L139" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="4:12" ht="30">
       <c r="D140" s="10" t="s">
         <v>184</v>
       </c>
@@ -16251,8 +14441,11 @@
       <c r="J140" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="141" spans="4:10" ht="30">
+      <c r="L140" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="4:12" ht="30">
       <c r="D141" s="10" t="s">
         <v>823</v>
       </c>
@@ -16274,8 +14467,11 @@
       <c r="J141" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="142" spans="4:10" ht="30">
+      <c r="L141" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="4:12" ht="30">
       <c r="D142" s="10" t="s">
         <v>824</v>
       </c>
@@ -16297,8 +14493,11 @@
       <c r="J142" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="143" spans="4:10" ht="30">
+      <c r="L142" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="4:12" ht="30">
       <c r="D143" s="10" t="s">
         <v>825</v>
       </c>
@@ -16320,8 +14519,11 @@
       <c r="J143" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="144" spans="4:10" ht="30">
+      <c r="L143" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="4:12" ht="30">
       <c r="D144" s="10" t="s">
         <v>187</v>
       </c>
@@ -16343,8 +14545,11 @@
       <c r="J144" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="145" spans="4:10" ht="30">
+      <c r="L144" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="4:12" ht="30">
       <c r="D145" s="10" t="s">
         <v>188</v>
       </c>
@@ -16366,8 +14571,11 @@
       <c r="J145" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="146" spans="4:10" ht="30">
+      <c r="L145" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="4:12" ht="30">
       <c r="D146" s="10" t="s">
         <v>117</v>
       </c>
@@ -16389,8 +14597,11 @@
       <c r="J146" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="147" spans="4:10" ht="30">
+      <c r="L146" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="4:12" ht="30">
       <c r="D147" s="10" t="s">
         <v>826</v>
       </c>
@@ -16412,8 +14623,11 @@
       <c r="J147" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="148" spans="4:10">
+      <c r="L147" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="4:12">
       <c r="D148" s="10" t="s">
         <v>264</v>
       </c>
@@ -16435,8 +14649,11 @@
       <c r="J148" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="149" spans="4:10">
+      <c r="L148" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="4:12">
       <c r="D149" s="10" t="s">
         <v>827</v>
       </c>
@@ -16458,8 +14675,11 @@
       <c r="J149" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="150" spans="4:10" ht="30">
+      <c r="L149" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="4:12" ht="30">
       <c r="D150" s="10" t="s">
         <v>828</v>
       </c>
@@ -16481,8 +14701,11 @@
       <c r="J150" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="151" spans="4:10" ht="30">
+      <c r="L150" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="4:12" ht="30">
       <c r="D151" s="10" t="s">
         <v>829</v>
       </c>
@@ -16504,8 +14727,11 @@
       <c r="J151" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="152" spans="4:10" ht="30">
+      <c r="L151" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="4:12" ht="30">
       <c r="D152" s="10" t="s">
         <v>830</v>
       </c>
@@ -16527,8 +14753,11 @@
       <c r="J152" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="153" spans="4:10" ht="30">
+      <c r="L152" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="4:12" ht="30">
       <c r="D153" s="10" t="s">
         <v>831</v>
       </c>
@@ -16550,8 +14779,11 @@
       <c r="J153" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="154" spans="4:10">
+      <c r="L153" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="4:12">
       <c r="D154" s="10" t="s">
         <v>832</v>
       </c>
@@ -16573,8 +14805,11 @@
       <c r="J154" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="155" spans="4:10" ht="30">
+      <c r="L154" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="4:12" ht="30">
       <c r="D155" s="10" t="s">
         <v>833</v>
       </c>
@@ -16596,8 +14831,11 @@
       <c r="J155" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="156" spans="4:10" ht="30">
+      <c r="L155" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="4:12" ht="30">
       <c r="D156" s="10" t="s">
         <v>834</v>
       </c>
@@ -16619,8 +14857,11 @@
       <c r="J156" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="157" spans="4:10" ht="30">
+      <c r="L156" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="4:12" ht="30">
       <c r="D157" s="10" t="s">
         <v>835</v>
       </c>
@@ -16642,8 +14883,11 @@
       <c r="J157" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="158" spans="4:10">
+      <c r="L157" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="4:12">
       <c r="D158" s="10" t="s">
         <v>227</v>
       </c>
@@ -16665,8 +14909,11 @@
       <c r="J158" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="159" spans="4:10">
+      <c r="L158" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="4:12">
       <c r="D159" s="10" t="s">
         <v>836</v>
       </c>
@@ -16688,8 +14935,11 @@
       <c r="J159" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="160" spans="4:10" ht="30">
+      <c r="L159" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="4:12" ht="30">
       <c r="D160" s="10" t="s">
         <v>837</v>
       </c>
@@ -16711,8 +14961,11 @@
       <c r="J160" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="161" spans="4:10" ht="30">
+      <c r="L160" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="4:12" ht="30">
       <c r="D161" s="10" t="s">
         <v>838</v>
       </c>
@@ -16734,8 +14987,11 @@
       <c r="J161" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="162" spans="4:10" ht="30">
+      <c r="L161" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="4:12" ht="30">
       <c r="D162" s="10" t="s">
         <v>839</v>
       </c>
@@ -16757,8 +15013,11 @@
       <c r="J162" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="163" spans="4:10">
+      <c r="L162" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="4:12">
       <c r="D163" s="10" t="s">
         <v>840</v>
       </c>
@@ -16780,8 +15039,11 @@
       <c r="J163" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="164" spans="4:10" ht="30">
+      <c r="L163" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="4:12" ht="30">
       <c r="D164" s="10" t="s">
         <v>841</v>
       </c>
@@ -16803,8 +15065,11 @@
       <c r="J164" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="165" spans="4:10" ht="30">
+      <c r="L164" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="4:12" ht="30">
       <c r="D165" s="10" t="s">
         <v>842</v>
       </c>
@@ -16826,8 +15091,11 @@
       <c r="J165" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="166" spans="4:10">
+      <c r="L165" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="4:12">
       <c r="D166" s="10" t="s">
         <v>843</v>
       </c>
@@ -16849,8 +15117,11 @@
       <c r="J166" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="167" spans="4:10" ht="30">
+      <c r="L166" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="4:12" ht="30">
       <c r="D167" s="10" t="s">
         <v>213</v>
       </c>
@@ -16872,8 +15143,11 @@
       <c r="J167" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="168" spans="4:10" ht="30">
+      <c r="L167" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="4:12" ht="30">
       <c r="D168" s="10" t="s">
         <v>844</v>
       </c>
@@ -16895,8 +15169,11 @@
       <c r="J168" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="169" spans="4:10" ht="30">
+      <c r="L168" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="4:12" ht="30">
       <c r="D169" s="10" t="s">
         <v>845</v>
       </c>
@@ -16918,8 +15195,11 @@
       <c r="J169" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="170" spans="4:10" ht="30">
+      <c r="L169" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="4:12" ht="30">
       <c r="D170" s="10" t="s">
         <v>846</v>
       </c>
@@ -16941,8 +15221,11 @@
       <c r="J170" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="171" spans="4:10" ht="30">
+      <c r="L170" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="4:12" ht="30">
       <c r="D171" s="10" t="s">
         <v>847</v>
       </c>
@@ -16964,8 +15247,11 @@
       <c r="J171" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="172" spans="4:10" ht="30">
+      <c r="L171" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="4:12" ht="30">
       <c r="D172" s="10" t="s">
         <v>58</v>
       </c>
@@ -16987,8 +15273,11 @@
       <c r="J172" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="173" spans="4:10">
+      <c r="L172" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="4:12">
       <c r="D173" s="10" t="s">
         <v>253</v>
       </c>
@@ -17010,8 +15299,11 @@
       <c r="J173" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="174" spans="4:10">
+      <c r="L173" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="4:12">
       <c r="D174" s="10" t="s">
         <v>255</v>
       </c>
@@ -17033,8 +15325,11 @@
       <c r="J174" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="175" spans="4:10">
+      <c r="L174" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="4:12">
       <c r="D175" s="10" t="s">
         <v>256</v>
       </c>
@@ -17056,8 +15351,11 @@
       <c r="J175" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="176" spans="4:10">
+      <c r="L175" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="4:12">
       <c r="D176" s="10" t="s">
         <v>258</v>
       </c>
@@ -17079,8 +15377,11 @@
       <c r="J176" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="177" spans="4:10">
+      <c r="L176" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="4:12">
       <c r="D177" s="10" t="s">
         <v>848</v>
       </c>
@@ -17102,8 +15403,11 @@
       <c r="J177" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="178" spans="4:10">
+      <c r="L177" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="4:12">
       <c r="D178" s="10" t="s">
         <v>849</v>
       </c>
@@ -17125,8 +15429,11 @@
       <c r="J178" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="179" spans="4:10">
+      <c r="L178" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="4:12">
       <c r="D179" s="10" t="s">
         <v>850</v>
       </c>
@@ -17148,8 +15455,11 @@
       <c r="J179" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="180" spans="4:10" ht="30">
+      <c r="L179" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="4:12" ht="30">
       <c r="D180" s="10" t="s">
         <v>851</v>
       </c>
@@ -17171,8 +15481,11 @@
       <c r="J180" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="181" spans="4:10" ht="30">
+      <c r="L180" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="4:12" ht="30">
       <c r="D181" s="10" t="s">
         <v>852</v>
       </c>
@@ -17194,260 +15507,381 @@
       <c r="J181" s="6" t="s">
         <v>775</v>
       </c>
+      <c r="L181" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="4:12" ht="30">
+      <c r="D182" s="12" t="s">
+        <v>857</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="F182" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G182" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="H182" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="I182" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="J182" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="L182" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="4:12" ht="30">
+      <c r="D183" s="12" t="s">
+        <v>858</v>
+      </c>
+      <c r="E183" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="F183" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G183" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="H183" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="I183" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="J183" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="L183" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="4:12" ht="30">
+      <c r="D184" s="12" t="s">
+        <v>859</v>
+      </c>
+      <c r="E184" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="F184" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G184" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="H184" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="I184" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="J184" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="L184" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="4:12" ht="30">
+      <c r="D185" s="12" t="s">
+        <v>860</v>
+      </c>
+      <c r="E185" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="F185" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="G185" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="H185" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="I185" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="J185" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="L185" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="4:12" ht="30">
+      <c r="D186" s="12" t="s">
+        <v>861</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="F186" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="G186" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="H186" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="I186" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="J186" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="L186" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="4:12" ht="30">
+      <c r="D187" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="E187" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="F187" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="G187" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="H187" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="I187" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="J187" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="L187" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="4:12" ht="30">
+      <c r="D188" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="E188" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G188" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="H188" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="I188" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="J188" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="L188" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="4:12" ht="30">
+      <c r="D189" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="E189" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="F189" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G189" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="H189" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="I189" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="J189" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="L189" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="4:12" ht="30">
+      <c r="D190" s="12" t="s">
+        <v>865</v>
+      </c>
+      <c r="E190" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="F190" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="G190" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="H190" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="I190" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="J190" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="L190" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="4:12" ht="30">
+      <c r="D191" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="F191" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="G191" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="H191" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I191" s="6" t="s">
+        <v>688</v>
+      </c>
+      <c r="J191" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="L191" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="4:12" ht="30">
+      <c r="D192" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="E192" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="F192" s="6" t="s">
+        <v>706</v>
+      </c>
+      <c r="G192" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="H192" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I192" s="6" t="s">
+        <v>688</v>
+      </c>
+      <c r="J192" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="L192" s="13" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E4:T73 E76:T181 E74:G75 I74:T75">
-    <cfRule type="cellIs" dxfId="163" priority="56" operator="equal">
+  <conditionalFormatting sqref="E4:X192">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+      <formula>"Estadounidense"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="2" operator="equal">
       <formula>"Italiana"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="3" operator="equal">
       <formula>"Francés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="161" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="4" operator="equal">
       <formula>"Pasta/Fideos"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="5" operator="equal">
       <formula>"Gourmet"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
       <formula>"Chino"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="61" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
       <formula>"Caldo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="8" operator="equal">
       <formula>"Mexicano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="9" operator="equal">
       <formula>"Para compartir"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="155" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="10" operator="equal">
       <formula>"Español"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="154" priority="65" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="11" operator="equal">
       <formula>"Arroz"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
       <formula>"Masa"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="152" priority="67" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
       <formula>"Patata"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="68" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="14" operator="equal">
       <formula>"Comida rápida"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="69" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
       <formula>"Vegano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="149" priority="70" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="16" operator="equal">
       <formula>"Peruano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="148" priority="71" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="17" operator="equal">
       <formula>"Picante"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="72" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="18" operator="equal">
       <formula>"Frito"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="146" priority="73" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="19" operator="equal">
       <formula>"Marisco"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="74" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="20" operator="equal">
       <formula>"Vegetariano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="75" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="21" operator="equal">
       <formula>"Japonés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="143" priority="76" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="22" operator="equal">
       <formula>"Desayuno"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="23" operator="equal">
       <formula>"Vegetales"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="78" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="24" operator="equal">
       <formula>"Carne"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="79" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="25" operator="equal">
       <formula>"Frío"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="80" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="26" operator="equal">
       <formula>"Crudo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="81" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="27" operator="equal">
       <formula>"Sushi"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="82" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="28" operator="equal">
       <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H75">
-    <cfRule type="cellIs" dxfId="136" priority="29" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="30" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="134" priority="31" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="32" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="33" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="34" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="35" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="36" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="37" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="38" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="39" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="40" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="41" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="42" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="43" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="44" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="45" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="46" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="47" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="48" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="49" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="50" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="51" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="52" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="53" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="54" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="55" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H74">
-    <cfRule type="cellIs" dxfId="109" priority="2" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="3" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="4" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="5" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="6" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="7" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="8" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="9" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="10" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="11" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="12" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="13" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="14" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="15" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="16" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="17" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="18" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="19" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="20" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="21" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="22" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="23" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="24" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="25" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="26" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="27" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="28" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4:T181">
-    <cfRule type="cellIs" dxfId="82" priority="1" operator="equal">
-      <formula>"Estadounidense"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17488,27 +15922,27 @@
     </row>
     <row r="4" spans="2:12">
       <c r="B4" s="7">
-        <f>COUNTIF(Platos!E4:J485,Recompte!B3)</f>
+        <f>COUNTIF(Platos!E4:J483,Recompte!B3)</f>
         <v>6</v>
       </c>
       <c r="D4" s="7">
-        <f>COUNTIF(Platos!E4:J485,D3)</f>
-        <v>20</v>
+        <f>COUNTIF(Platos!E4:J483,D3)</f>
+        <v>21</v>
       </c>
       <c r="F4" s="7">
-        <f>COUNTIF(Platos!E4:J485,F3)</f>
+        <f>COUNTIF(Platos!E4:J483,F3)</f>
         <v>18</v>
       </c>
       <c r="H4" s="7">
-        <f>COUNTIF(Platos!E4:J485,H3)</f>
+        <f>COUNTIF(Platos!E4:J483,H3)</f>
         <v>24</v>
       </c>
       <c r="J4" s="7">
-        <f>COUNTIF(Platos!E4:J485,J3)</f>
+        <f>COUNTIF(Platos!E4:J483,J3)</f>
         <v>28</v>
       </c>
       <c r="L4" s="7">
-        <f>COUNTIF(Platos!E4:J485,L3)</f>
+        <f>COUNTIF(Platos!E4:J483,L3)</f>
         <v>9</v>
       </c>
     </row>
@@ -17534,28 +15968,28 @@
     </row>
     <row r="7" spans="2:12">
       <c r="B7" s="7">
-        <f>COUNTIF(Platos!E4:J485,B6)</f>
-        <v>20</v>
+        <f>COUNTIF(Platos!E4:J483,B6)</f>
+        <v>23</v>
       </c>
       <c r="D7" s="7">
-        <f>COUNTIF(Platos!E4:J485,D6)</f>
-        <v>44</v>
+        <f>COUNTIF(Platos!E4:J483,D6)</f>
+        <v>46</v>
       </c>
       <c r="F7" s="7">
-        <f>COUNTIF(Platos!E4:J485,F6)</f>
+        <f>COUNTIF(Platos!E4:J483,F6)</f>
         <v>18</v>
       </c>
       <c r="H7" s="7">
-        <f>COUNTIF(Platos!E4:J485,H6)</f>
-        <v>14</v>
+        <f>COUNTIF(Platos!E4:J483,H6)</f>
+        <v>15</v>
       </c>
       <c r="J7" s="7">
-        <f>COUNTIF(Platos!E4:J485,J6)</f>
-        <v>63</v>
+        <f>COUNTIF(Platos!E4:J483,J6)</f>
+        <v>70</v>
       </c>
       <c r="L7" s="7">
-        <f>COUNTIF(Platos!E4:J485,L6)</f>
-        <v>23</v>
+        <f>COUNTIF(Platos!E4:J483,L6)</f>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="30">
@@ -17580,27 +16014,27 @@
     </row>
     <row r="10" spans="2:12">
       <c r="B10" s="7">
-        <f>COUNTIF(Platos!E4:J485,B9)</f>
+        <f>COUNTIF(Platos!E4:J483,B9)</f>
         <v>18</v>
       </c>
       <c r="D10" s="7">
-        <f>COUNTIF(Platos!E4:J485,D9)</f>
-        <v>24</v>
+        <f>COUNTIF(Platos!E4:J483,D9)</f>
+        <v>26</v>
       </c>
       <c r="F10" s="7">
-        <f>COUNTIF(Platos!E4:J485,F9)</f>
+        <f>COUNTIF(Platos!E4:J483,F9)</f>
         <v>14</v>
       </c>
       <c r="H10" s="7">
-        <f>COUNTIF(Platos!E4:J485,H9)</f>
-        <v>31</v>
+        <f>COUNTIF(Platos!E4:J483,H9)</f>
+        <v>35</v>
       </c>
       <c r="J10" s="7">
-        <f>COUNTIF(Platos!E4:J485,J9)</f>
-        <v>48</v>
+        <f>COUNTIF(Platos!E4:J483,J9)</f>
+        <v>55</v>
       </c>
       <c r="L10" s="7">
-        <f>COUNTIF(Platos!E4:J485,L9)</f>
+        <f>COUNTIF(Platos!E4:J483,L9)</f>
         <v>16</v>
       </c>
     </row>
@@ -17626,28 +16060,28 @@
     </row>
     <row r="13" spans="2:12">
       <c r="B13" s="7">
-        <f>COUNTIF(Platos!E4:J485,B12)</f>
+        <f>COUNTIF(Platos!E4:J483,B12)</f>
         <v>23</v>
       </c>
       <c r="D13" s="7">
-        <f>COUNTIF(Platos!E4:J485,D12)</f>
+        <f>COUNTIF(Platos!E4:J483,D12)</f>
         <v>57</v>
       </c>
       <c r="F13" s="7">
-        <f>COUNTIF(Platos!E4:J485,F12)</f>
+        <f>COUNTIF(Platos!E4:J483,F12)</f>
         <v>16</v>
       </c>
       <c r="H13" s="7">
-        <f>COUNTIF(Platos!E4:J485,H12)</f>
+        <f>COUNTIF(Platos!E4:J483,H12)</f>
         <v>19</v>
       </c>
       <c r="J13" s="7">
-        <f>COUNTIF(Platos!E4:J485,J12)</f>
+        <f>COUNTIF(Platos!E4:J483,J12)</f>
         <v>18</v>
       </c>
       <c r="L13" s="7">
-        <f>COUNTIF(Platos!E4:J485,L12)</f>
-        <v>17</v>
+        <f>COUNTIF(Platos!E4:J483,L12)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="2:12">
@@ -17663,2174 +16097,2174 @@
     </row>
     <row r="16" spans="2:12">
       <c r="B16" s="7">
-        <f>COUNTIF(Platos!E4:J485,B15)</f>
+        <f>COUNTIF(Platos!E4:J483,B15)</f>
         <v>20</v>
       </c>
       <c r="D16" s="7">
-        <f>COUNTIF(Platos!E4:J485,D15)</f>
-        <v>34</v>
+        <f>COUNTIF(Platos!E4:J483,D15)</f>
+        <v>38</v>
       </c>
       <c r="F16" s="7">
-        <f>COUNTIF(Platos!E4:J485,F15)</f>
-        <v>9</v>
+        <f>COUNTIF(Platos!E4:J483,F15)</f>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3">
-    <cfRule type="cellIs" dxfId="946" priority="703" operator="equal">
+    <cfRule type="cellIs" dxfId="729" priority="703" operator="equal">
       <formula>"Italiana"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="945" priority="704" operator="equal">
+    <cfRule type="cellIs" dxfId="728" priority="704" operator="equal">
       <formula>"Francés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="944" priority="705" operator="equal">
+    <cfRule type="cellIs" dxfId="727" priority="705" operator="equal">
       <formula>"Pasta/Fideos"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="943" priority="706" operator="equal">
+    <cfRule type="cellIs" dxfId="726" priority="706" operator="equal">
       <formula>"Gourmet"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="942" priority="707" operator="equal">
+    <cfRule type="cellIs" dxfId="725" priority="707" operator="equal">
       <formula>"Chino"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="941" priority="708" operator="equal">
+    <cfRule type="cellIs" dxfId="724" priority="708" operator="equal">
       <formula>"Caldo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="940" priority="709" operator="equal">
+    <cfRule type="cellIs" dxfId="723" priority="709" operator="equal">
       <formula>"Mexicano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="939" priority="710" operator="equal">
+    <cfRule type="cellIs" dxfId="722" priority="710" operator="equal">
       <formula>"Para compartir"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="938" priority="711" operator="equal">
+    <cfRule type="cellIs" dxfId="721" priority="711" operator="equal">
       <formula>"Español"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="937" priority="712" operator="equal">
+    <cfRule type="cellIs" dxfId="720" priority="712" operator="equal">
       <formula>"Arroz"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="936" priority="713" operator="equal">
+    <cfRule type="cellIs" dxfId="719" priority="713" operator="equal">
       <formula>"Masa"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="935" priority="714" operator="equal">
+    <cfRule type="cellIs" dxfId="718" priority="714" operator="equal">
       <formula>"Patata"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="934" priority="715" operator="equal">
+    <cfRule type="cellIs" dxfId="717" priority="715" operator="equal">
       <formula>"Comida rápida"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="933" priority="716" operator="equal">
+    <cfRule type="cellIs" dxfId="716" priority="716" operator="equal">
       <formula>"Vegano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="932" priority="717" operator="equal">
+    <cfRule type="cellIs" dxfId="715" priority="717" operator="equal">
       <formula>"Peruano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="931" priority="718" operator="equal">
+    <cfRule type="cellIs" dxfId="714" priority="718" operator="equal">
       <formula>"Picante"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="930" priority="719" operator="equal">
+    <cfRule type="cellIs" dxfId="713" priority="719" operator="equal">
       <formula>"Frito"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="929" priority="720" operator="equal">
+    <cfRule type="cellIs" dxfId="712" priority="720" operator="equal">
       <formula>"Marisco"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="928" priority="721" operator="equal">
+    <cfRule type="cellIs" dxfId="711" priority="721" operator="equal">
       <formula>"Vegetariano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="927" priority="722" operator="equal">
+    <cfRule type="cellIs" dxfId="710" priority="722" operator="equal">
       <formula>"Japonés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="926" priority="723" operator="equal">
+    <cfRule type="cellIs" dxfId="709" priority="723" operator="equal">
       <formula>"Desayuno"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="925" priority="724" operator="equal">
+    <cfRule type="cellIs" dxfId="708" priority="724" operator="equal">
       <formula>"Vegetales"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="924" priority="725" operator="equal">
+    <cfRule type="cellIs" dxfId="707" priority="725" operator="equal">
       <formula>"Carne"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="923" priority="726" operator="equal">
+    <cfRule type="cellIs" dxfId="706" priority="726" operator="equal">
       <formula>"Frío"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="922" priority="727" operator="equal">
+    <cfRule type="cellIs" dxfId="705" priority="727" operator="equal">
       <formula>"Crudo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="921" priority="728" operator="equal">
+    <cfRule type="cellIs" dxfId="704" priority="728" operator="equal">
       <formula>"Sushi"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="920" priority="729" operator="equal">
+    <cfRule type="cellIs" dxfId="703" priority="729" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="cellIs" dxfId="702" priority="541" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="701" priority="542" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="700" priority="543" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="699" priority="544" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="698" priority="545" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="697" priority="546" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="696" priority="547" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="695" priority="548" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="694" priority="549" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="693" priority="550" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="692" priority="551" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="691" priority="552" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="690" priority="553" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="689" priority="554" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="688" priority="555" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="687" priority="556" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="686" priority="557" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="685" priority="558" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="684" priority="559" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="683" priority="560" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="682" priority="561" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="681" priority="562" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="680" priority="563" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="679" priority="564" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="678" priority="565" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="677" priority="566" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="676" priority="567" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9">
+    <cfRule type="cellIs" dxfId="675" priority="379" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="674" priority="380" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="673" priority="381" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="672" priority="382" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="671" priority="383" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="670" priority="384" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="669" priority="385" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="668" priority="386" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="667" priority="387" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="666" priority="388" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="665" priority="389" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="664" priority="390" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="663" priority="391" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="662" priority="392" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="661" priority="393" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="660" priority="394" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="659" priority="395" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="658" priority="396" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="657" priority="397" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="656" priority="398" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="655" priority="399" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="654" priority="400" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="653" priority="401" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="652" priority="402" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="651" priority="403" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="650" priority="404" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="649" priority="405" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="cellIs" dxfId="648" priority="217" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="647" priority="218" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="646" priority="219" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="645" priority="220" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="644" priority="221" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="643" priority="222" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="642" priority="223" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="641" priority="224" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="640" priority="225" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="639" priority="226" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="638" priority="227" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="637" priority="228" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="636" priority="229" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="635" priority="230" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="634" priority="231" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="633" priority="232" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="632" priority="233" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="631" priority="234" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="630" priority="235" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="629" priority="236" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="628" priority="237" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="627" priority="238" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="626" priority="239" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="625" priority="240" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="624" priority="241" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="623" priority="242" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="622" priority="243" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="cellIs" dxfId="621" priority="55" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="620" priority="56" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="619" priority="57" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="618" priority="58" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="617" priority="59" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="616" priority="60" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="615" priority="61" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="614" priority="62" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="613" priority="63" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="612" priority="64" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="611" priority="65" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="610" priority="66" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="609" priority="67" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="608" priority="68" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="607" priority="69" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="606" priority="70" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="605" priority="71" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="604" priority="72" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="603" priority="73" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="602" priority="74" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="601" priority="75" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="600" priority="76" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="599" priority="77" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="598" priority="78" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="597" priority="79" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="596" priority="80" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="595" priority="81" operator="equal">
       <formula>"Pescado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3">
-    <cfRule type="cellIs" dxfId="919" priority="676" operator="equal">
+    <cfRule type="cellIs" dxfId="594" priority="676" operator="equal">
       <formula>"Italiana"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="918" priority="677" operator="equal">
+    <cfRule type="cellIs" dxfId="593" priority="677" operator="equal">
       <formula>"Francés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="917" priority="678" operator="equal">
+    <cfRule type="cellIs" dxfId="592" priority="678" operator="equal">
       <formula>"Pasta/Fideos"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="916" priority="679" operator="equal">
+    <cfRule type="cellIs" dxfId="591" priority="679" operator="equal">
       <formula>"Gourmet"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="915" priority="680" operator="equal">
+    <cfRule type="cellIs" dxfId="590" priority="680" operator="equal">
       <formula>"Chino"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="914" priority="681" operator="equal">
+    <cfRule type="cellIs" dxfId="589" priority="681" operator="equal">
       <formula>"Caldo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="913" priority="682" operator="equal">
+    <cfRule type="cellIs" dxfId="588" priority="682" operator="equal">
       <formula>"Mexicano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="912" priority="683" operator="equal">
+    <cfRule type="cellIs" dxfId="587" priority="683" operator="equal">
       <formula>"Para compartir"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="911" priority="684" operator="equal">
+    <cfRule type="cellIs" dxfId="586" priority="684" operator="equal">
       <formula>"Español"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="910" priority="685" operator="equal">
+    <cfRule type="cellIs" dxfId="585" priority="685" operator="equal">
       <formula>"Arroz"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="909" priority="686" operator="equal">
+    <cfRule type="cellIs" dxfId="584" priority="686" operator="equal">
       <formula>"Masa"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="908" priority="687" operator="equal">
+    <cfRule type="cellIs" dxfId="583" priority="687" operator="equal">
       <formula>"Patata"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="907" priority="688" operator="equal">
+    <cfRule type="cellIs" dxfId="582" priority="688" operator="equal">
       <formula>"Comida rápida"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="906" priority="689" operator="equal">
+    <cfRule type="cellIs" dxfId="581" priority="689" operator="equal">
       <formula>"Vegano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="905" priority="690" operator="equal">
+    <cfRule type="cellIs" dxfId="580" priority="690" operator="equal">
       <formula>"Peruano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="904" priority="691" operator="equal">
+    <cfRule type="cellIs" dxfId="579" priority="691" operator="equal">
       <formula>"Picante"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="903" priority="692" operator="equal">
+    <cfRule type="cellIs" dxfId="578" priority="692" operator="equal">
       <formula>"Frito"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="902" priority="693" operator="equal">
+    <cfRule type="cellIs" dxfId="577" priority="693" operator="equal">
       <formula>"Marisco"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="901" priority="694" operator="equal">
+    <cfRule type="cellIs" dxfId="576" priority="694" operator="equal">
       <formula>"Vegetariano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="900" priority="695" operator="equal">
+    <cfRule type="cellIs" dxfId="575" priority="695" operator="equal">
       <formula>"Japonés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="899" priority="696" operator="equal">
+    <cfRule type="cellIs" dxfId="574" priority="696" operator="equal">
       <formula>"Desayuno"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="898" priority="697" operator="equal">
+    <cfRule type="cellIs" dxfId="573" priority="697" operator="equal">
       <formula>"Vegetales"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="897" priority="698" operator="equal">
+    <cfRule type="cellIs" dxfId="572" priority="698" operator="equal">
       <formula>"Carne"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="896" priority="699" operator="equal">
+    <cfRule type="cellIs" dxfId="571" priority="699" operator="equal">
       <formula>"Frío"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="895" priority="700" operator="equal">
+    <cfRule type="cellIs" dxfId="570" priority="700" operator="equal">
       <formula>"Crudo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="894" priority="701" operator="equal">
+    <cfRule type="cellIs" dxfId="569" priority="701" operator="equal">
       <formula>"Sushi"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="893" priority="702" operator="equal">
+    <cfRule type="cellIs" dxfId="568" priority="702" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="cellIs" dxfId="567" priority="514" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="566" priority="515" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="565" priority="516" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="564" priority="517" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="563" priority="518" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="562" priority="519" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="561" priority="520" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="560" priority="521" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="559" priority="522" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="558" priority="523" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="557" priority="524" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="556" priority="525" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="555" priority="526" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="554" priority="527" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="553" priority="528" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="552" priority="529" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="551" priority="530" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="550" priority="531" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="549" priority="532" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="548" priority="533" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="547" priority="534" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="546" priority="535" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="545" priority="536" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="544" priority="537" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="543" priority="538" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="542" priority="539" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="541" priority="540" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9">
+    <cfRule type="cellIs" dxfId="540" priority="352" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="539" priority="353" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="538" priority="354" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="537" priority="355" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="536" priority="356" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="535" priority="357" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="534" priority="358" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="533" priority="359" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="532" priority="360" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="531" priority="361" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="530" priority="362" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="529" priority="363" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="528" priority="364" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="527" priority="365" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="526" priority="366" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="525" priority="367" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="524" priority="368" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="523" priority="369" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="522" priority="370" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="521" priority="371" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="520" priority="372" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="519" priority="373" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="518" priority="374" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="517" priority="375" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="516" priority="376" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="515" priority="377" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="514" priority="378" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D12">
+    <cfRule type="cellIs" dxfId="513" priority="190" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="512" priority="191" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="511" priority="192" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="510" priority="193" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="509" priority="194" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="508" priority="195" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="507" priority="196" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="506" priority="197" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="505" priority="198" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="504" priority="199" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="503" priority="200" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="502" priority="201" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="501" priority="202" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="500" priority="203" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="499" priority="204" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="498" priority="205" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="497" priority="206" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="496" priority="207" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="495" priority="208" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="494" priority="209" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="493" priority="210" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="492" priority="211" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="491" priority="212" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="490" priority="213" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="489" priority="214" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="488" priority="215" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="487" priority="216" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="cellIs" dxfId="486" priority="28" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="485" priority="29" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="484" priority="30" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="483" priority="31" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="482" priority="32" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="481" priority="33" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="480" priority="34" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="479" priority="35" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="478" priority="36" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="477" priority="37" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="476" priority="38" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="475" priority="39" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="474" priority="40" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="473" priority="41" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="472" priority="42" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="471" priority="43" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="470" priority="44" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="469" priority="45" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="468" priority="46" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="467" priority="47" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="466" priority="48" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="465" priority="49" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="464" priority="50" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="463" priority="51" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="462" priority="52" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="461" priority="53" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="460" priority="54" operator="equal">
       <formula>"Pescado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
-    <cfRule type="cellIs" dxfId="892" priority="649" operator="equal">
+    <cfRule type="cellIs" dxfId="459" priority="649" operator="equal">
       <formula>"Italiana"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="891" priority="650" operator="equal">
+    <cfRule type="cellIs" dxfId="458" priority="650" operator="equal">
       <formula>"Francés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="890" priority="651" operator="equal">
+    <cfRule type="cellIs" dxfId="457" priority="651" operator="equal">
       <formula>"Pasta/Fideos"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="889" priority="652" operator="equal">
+    <cfRule type="cellIs" dxfId="456" priority="652" operator="equal">
       <formula>"Gourmet"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="888" priority="653" operator="equal">
+    <cfRule type="cellIs" dxfId="455" priority="653" operator="equal">
       <formula>"Chino"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="887" priority="654" operator="equal">
+    <cfRule type="cellIs" dxfId="454" priority="654" operator="equal">
       <formula>"Caldo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="886" priority="655" operator="equal">
+    <cfRule type="cellIs" dxfId="453" priority="655" operator="equal">
       <formula>"Mexicano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="885" priority="656" operator="equal">
+    <cfRule type="cellIs" dxfId="452" priority="656" operator="equal">
       <formula>"Para compartir"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="884" priority="657" operator="equal">
+    <cfRule type="cellIs" dxfId="451" priority="657" operator="equal">
       <formula>"Español"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="883" priority="658" operator="equal">
+    <cfRule type="cellIs" dxfId="450" priority="658" operator="equal">
       <formula>"Arroz"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="882" priority="659" operator="equal">
+    <cfRule type="cellIs" dxfId="449" priority="659" operator="equal">
       <formula>"Masa"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="881" priority="660" operator="equal">
+    <cfRule type="cellIs" dxfId="448" priority="660" operator="equal">
       <formula>"Patata"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="880" priority="661" operator="equal">
+    <cfRule type="cellIs" dxfId="447" priority="661" operator="equal">
       <formula>"Comida rápida"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="879" priority="662" operator="equal">
+    <cfRule type="cellIs" dxfId="446" priority="662" operator="equal">
       <formula>"Vegano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="878" priority="663" operator="equal">
+    <cfRule type="cellIs" dxfId="445" priority="663" operator="equal">
       <formula>"Peruano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="877" priority="664" operator="equal">
+    <cfRule type="cellIs" dxfId="444" priority="664" operator="equal">
       <formula>"Picante"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="876" priority="665" operator="equal">
+    <cfRule type="cellIs" dxfId="443" priority="665" operator="equal">
       <formula>"Frito"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="875" priority="666" operator="equal">
+    <cfRule type="cellIs" dxfId="442" priority="666" operator="equal">
       <formula>"Marisco"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="874" priority="667" operator="equal">
+    <cfRule type="cellIs" dxfId="441" priority="667" operator="equal">
       <formula>"Vegetariano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="873" priority="668" operator="equal">
+    <cfRule type="cellIs" dxfId="440" priority="668" operator="equal">
       <formula>"Japonés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="872" priority="669" operator="equal">
+    <cfRule type="cellIs" dxfId="439" priority="669" operator="equal">
       <formula>"Desayuno"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="871" priority="670" operator="equal">
+    <cfRule type="cellIs" dxfId="438" priority="670" operator="equal">
       <formula>"Vegetales"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="870" priority="671" operator="equal">
+    <cfRule type="cellIs" dxfId="437" priority="671" operator="equal">
       <formula>"Carne"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="869" priority="672" operator="equal">
+    <cfRule type="cellIs" dxfId="436" priority="672" operator="equal">
       <formula>"Frío"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="868" priority="673" operator="equal">
+    <cfRule type="cellIs" dxfId="435" priority="673" operator="equal">
       <formula>"Crudo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="867" priority="674" operator="equal">
+    <cfRule type="cellIs" dxfId="434" priority="674" operator="equal">
       <formula>"Sushi"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="866" priority="675" operator="equal">
+    <cfRule type="cellIs" dxfId="433" priority="675" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="cellIs" dxfId="432" priority="1" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="431" priority="2" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="430" priority="3" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="429" priority="4" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="428" priority="5" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="427" priority="6" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="426" priority="7" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="425" priority="8" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="424" priority="9" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="423" priority="10" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="422" priority="11" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="421" priority="12" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="420" priority="13" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="419" priority="14" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="418" priority="15" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="417" priority="16" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="416" priority="17" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="415" priority="18" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="414" priority="19" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="413" priority="20" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="412" priority="21" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="411" priority="22" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="410" priority="23" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="409" priority="24" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="408" priority="25" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="407" priority="26" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="406" priority="27" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9">
+    <cfRule type="cellIs" dxfId="405" priority="325" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="404" priority="326" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="403" priority="327" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="402" priority="328" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="401" priority="329" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="400" priority="330" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="399" priority="331" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="398" priority="332" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="397" priority="333" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="396" priority="334" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="395" priority="335" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="394" priority="336" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="393" priority="337" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="392" priority="338" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="391" priority="339" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="390" priority="340" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="389" priority="341" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="388" priority="342" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="387" priority="343" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="386" priority="344" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="385" priority="345" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="384" priority="346" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="383" priority="347" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="382" priority="348" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="381" priority="349" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="380" priority="350" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="379" priority="351" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="cellIs" dxfId="378" priority="163" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="377" priority="164" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="376" priority="165" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="375" priority="166" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="374" priority="167" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="373" priority="168" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="372" priority="169" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="371" priority="170" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="370" priority="171" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="369" priority="172" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="368" priority="173" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="367" priority="174" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="366" priority="175" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="365" priority="176" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="364" priority="177" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="363" priority="178" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="362" priority="179" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="361" priority="180" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="360" priority="181" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="359" priority="182" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="358" priority="183" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="357" priority="184" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="356" priority="185" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="355" priority="186" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="354" priority="187" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="353" priority="188" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="352" priority="189" operator="equal">
       <formula>"Pescado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="cellIs" dxfId="865" priority="622" operator="equal">
+    <cfRule type="cellIs" dxfId="351" priority="622" operator="equal">
       <formula>"Italiana"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="864" priority="623" operator="equal">
+    <cfRule type="cellIs" dxfId="350" priority="623" operator="equal">
       <formula>"Francés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="863" priority="624" operator="equal">
+    <cfRule type="cellIs" dxfId="349" priority="624" operator="equal">
       <formula>"Pasta/Fideos"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="862" priority="625" operator="equal">
+    <cfRule type="cellIs" dxfId="348" priority="625" operator="equal">
       <formula>"Gourmet"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="861" priority="626" operator="equal">
+    <cfRule type="cellIs" dxfId="347" priority="626" operator="equal">
       <formula>"Chino"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="860" priority="627" operator="equal">
+    <cfRule type="cellIs" dxfId="346" priority="627" operator="equal">
       <formula>"Caldo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="859" priority="628" operator="equal">
+    <cfRule type="cellIs" dxfId="345" priority="628" operator="equal">
       <formula>"Mexicano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="858" priority="629" operator="equal">
+    <cfRule type="cellIs" dxfId="344" priority="629" operator="equal">
       <formula>"Para compartir"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="857" priority="630" operator="equal">
+    <cfRule type="cellIs" dxfId="343" priority="630" operator="equal">
       <formula>"Español"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="856" priority="631" operator="equal">
+    <cfRule type="cellIs" dxfId="342" priority="631" operator="equal">
       <formula>"Arroz"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="855" priority="632" operator="equal">
+    <cfRule type="cellIs" dxfId="341" priority="632" operator="equal">
       <formula>"Masa"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="854" priority="633" operator="equal">
+    <cfRule type="cellIs" dxfId="340" priority="633" operator="equal">
       <formula>"Patata"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="853" priority="634" operator="equal">
+    <cfRule type="cellIs" dxfId="339" priority="634" operator="equal">
       <formula>"Comida rápida"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="852" priority="635" operator="equal">
+    <cfRule type="cellIs" dxfId="338" priority="635" operator="equal">
       <formula>"Vegano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="851" priority="636" operator="equal">
+    <cfRule type="cellIs" dxfId="337" priority="636" operator="equal">
       <formula>"Peruano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="850" priority="637" operator="equal">
+    <cfRule type="cellIs" dxfId="336" priority="637" operator="equal">
       <formula>"Picante"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="849" priority="638" operator="equal">
+    <cfRule type="cellIs" dxfId="335" priority="638" operator="equal">
       <formula>"Frito"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="848" priority="639" operator="equal">
+    <cfRule type="cellIs" dxfId="334" priority="639" operator="equal">
       <formula>"Marisco"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="847" priority="640" operator="equal">
+    <cfRule type="cellIs" dxfId="333" priority="640" operator="equal">
       <formula>"Vegetariano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="846" priority="641" operator="equal">
+    <cfRule type="cellIs" dxfId="332" priority="641" operator="equal">
       <formula>"Japonés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="845" priority="642" operator="equal">
+    <cfRule type="cellIs" dxfId="331" priority="642" operator="equal">
       <formula>"Desayuno"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="844" priority="643" operator="equal">
+    <cfRule type="cellIs" dxfId="330" priority="643" operator="equal">
       <formula>"Vegetales"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="843" priority="644" operator="equal">
+    <cfRule type="cellIs" dxfId="329" priority="644" operator="equal">
       <formula>"Carne"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="842" priority="645" operator="equal">
+    <cfRule type="cellIs" dxfId="328" priority="645" operator="equal">
       <formula>"Frío"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="841" priority="646" operator="equal">
+    <cfRule type="cellIs" dxfId="327" priority="646" operator="equal">
       <formula>"Crudo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="840" priority="647" operator="equal">
+    <cfRule type="cellIs" dxfId="326" priority="647" operator="equal">
       <formula>"Sushi"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="839" priority="648" operator="equal">
+    <cfRule type="cellIs" dxfId="325" priority="648" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
+    <cfRule type="cellIs" dxfId="324" priority="460" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="323" priority="461" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="322" priority="462" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="321" priority="463" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="320" priority="464" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="319" priority="465" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="318" priority="466" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="317" priority="467" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="316" priority="468" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="315" priority="469" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="314" priority="470" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="313" priority="471" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="312" priority="472" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="311" priority="473" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="310" priority="474" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="309" priority="475" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="308" priority="476" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="307" priority="477" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="306" priority="478" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="305" priority="479" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="304" priority="480" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="303" priority="481" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="302" priority="482" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="301" priority="483" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="300" priority="484" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="299" priority="485" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="298" priority="486" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H9">
+    <cfRule type="cellIs" dxfId="297" priority="298" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="296" priority="299" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="295" priority="300" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="294" priority="301" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="293" priority="302" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="292" priority="303" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="291" priority="304" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="290" priority="305" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="289" priority="306" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="288" priority="307" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="287" priority="308" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="286" priority="309" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="285" priority="310" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="284" priority="311" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="283" priority="312" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="282" priority="313" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="281" priority="314" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="280" priority="315" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="279" priority="316" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="278" priority="317" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="277" priority="318" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="276" priority="319" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="275" priority="320" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="274" priority="321" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="273" priority="322" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="272" priority="323" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="271" priority="324" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="cellIs" dxfId="270" priority="136" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="269" priority="137" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="268" priority="138" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="267" priority="139" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="266" priority="140" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="265" priority="141" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="264" priority="142" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="263" priority="143" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="262" priority="144" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="261" priority="145" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="260" priority="146" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="259" priority="147" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="258" priority="148" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="257" priority="149" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="256" priority="150" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="255" priority="151" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="254" priority="152" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="253" priority="153" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="252" priority="154" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="251" priority="155" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="250" priority="156" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="249" priority="157" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="248" priority="158" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="247" priority="159" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="246" priority="160" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="245" priority="161" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="244" priority="162" operator="equal">
       <formula>"Pescado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3">
-    <cfRule type="cellIs" dxfId="838" priority="595" operator="equal">
+    <cfRule type="cellIs" dxfId="243" priority="595" operator="equal">
       <formula>"Italiana"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="837" priority="596" operator="equal">
+    <cfRule type="cellIs" dxfId="242" priority="596" operator="equal">
       <formula>"Francés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="836" priority="597" operator="equal">
+    <cfRule type="cellIs" dxfId="241" priority="597" operator="equal">
       <formula>"Pasta/Fideos"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="835" priority="598" operator="equal">
+    <cfRule type="cellIs" dxfId="240" priority="598" operator="equal">
       <formula>"Gourmet"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="834" priority="599" operator="equal">
+    <cfRule type="cellIs" dxfId="239" priority="599" operator="equal">
       <formula>"Chino"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="833" priority="600" operator="equal">
+    <cfRule type="cellIs" dxfId="238" priority="600" operator="equal">
       <formula>"Caldo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="832" priority="601" operator="equal">
+    <cfRule type="cellIs" dxfId="237" priority="601" operator="equal">
       <formula>"Mexicano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="831" priority="602" operator="equal">
+    <cfRule type="cellIs" dxfId="236" priority="602" operator="equal">
       <formula>"Para compartir"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="830" priority="603" operator="equal">
+    <cfRule type="cellIs" dxfId="235" priority="603" operator="equal">
       <formula>"Español"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="829" priority="604" operator="equal">
+    <cfRule type="cellIs" dxfId="234" priority="604" operator="equal">
       <formula>"Arroz"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="828" priority="605" operator="equal">
+    <cfRule type="cellIs" dxfId="233" priority="605" operator="equal">
       <formula>"Masa"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="827" priority="606" operator="equal">
+    <cfRule type="cellIs" dxfId="232" priority="606" operator="equal">
       <formula>"Patata"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="826" priority="607" operator="equal">
+    <cfRule type="cellIs" dxfId="231" priority="607" operator="equal">
       <formula>"Comida rápida"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="825" priority="608" operator="equal">
+    <cfRule type="cellIs" dxfId="230" priority="608" operator="equal">
       <formula>"Vegano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="824" priority="609" operator="equal">
+    <cfRule type="cellIs" dxfId="229" priority="609" operator="equal">
       <formula>"Peruano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="823" priority="610" operator="equal">
+    <cfRule type="cellIs" dxfId="228" priority="610" operator="equal">
       <formula>"Picante"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="822" priority="611" operator="equal">
+    <cfRule type="cellIs" dxfId="227" priority="611" operator="equal">
       <formula>"Frito"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="821" priority="612" operator="equal">
+    <cfRule type="cellIs" dxfId="226" priority="612" operator="equal">
       <formula>"Marisco"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="820" priority="613" operator="equal">
+    <cfRule type="cellIs" dxfId="225" priority="613" operator="equal">
       <formula>"Vegetariano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="819" priority="614" operator="equal">
+    <cfRule type="cellIs" dxfId="224" priority="614" operator="equal">
       <formula>"Japonés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="818" priority="615" operator="equal">
+    <cfRule type="cellIs" dxfId="223" priority="615" operator="equal">
       <formula>"Desayuno"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="817" priority="616" operator="equal">
+    <cfRule type="cellIs" dxfId="222" priority="616" operator="equal">
       <formula>"Vegetales"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="816" priority="617" operator="equal">
+    <cfRule type="cellIs" dxfId="221" priority="617" operator="equal">
       <formula>"Carne"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="815" priority="618" operator="equal">
+    <cfRule type="cellIs" dxfId="220" priority="618" operator="equal">
       <formula>"Frío"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="814" priority="619" operator="equal">
+    <cfRule type="cellIs" dxfId="219" priority="619" operator="equal">
       <formula>"Crudo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="813" priority="620" operator="equal">
+    <cfRule type="cellIs" dxfId="218" priority="620" operator="equal">
       <formula>"Sushi"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="812" priority="621" operator="equal">
+    <cfRule type="cellIs" dxfId="217" priority="621" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6">
+    <cfRule type="cellIs" dxfId="216" priority="433" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="215" priority="434" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="214" priority="435" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="213" priority="436" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="212" priority="437" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="211" priority="438" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="210" priority="439" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="209" priority="440" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="208" priority="441" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="207" priority="442" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="206" priority="443" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="205" priority="444" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="204" priority="445" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="203" priority="446" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="202" priority="447" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="201" priority="448" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="200" priority="449" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="199" priority="450" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="198" priority="451" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="197" priority="452" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="196" priority="453" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="195" priority="454" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="194" priority="455" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="193" priority="456" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="192" priority="457" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="191" priority="458" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="190" priority="459" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J9">
+    <cfRule type="cellIs" dxfId="189" priority="271" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="188" priority="272" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="187" priority="273" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="186" priority="274" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="185" priority="275" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="184" priority="276" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="183" priority="277" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="182" priority="278" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="181" priority="279" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="180" priority="280" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="179" priority="281" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="178" priority="282" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="177" priority="283" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="176" priority="284" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="175" priority="285" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="174" priority="286" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="173" priority="287" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="172" priority="288" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="171" priority="289" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="170" priority="290" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="169" priority="291" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="168" priority="292" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="167" priority="293" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="166" priority="294" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="165" priority="295" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="164" priority="296" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="163" priority="297" operator="equal">
+      <formula>"Pescado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J12">
+    <cfRule type="cellIs" dxfId="162" priority="109" operator="equal">
+      <formula>"Italiana"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="161" priority="110" operator="equal">
+      <formula>"Francés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="160" priority="111" operator="equal">
+      <formula>"Pasta/Fideos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="159" priority="112" operator="equal">
+      <formula>"Gourmet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="158" priority="113" operator="equal">
+      <formula>"Chino"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="157" priority="114" operator="equal">
+      <formula>"Caldo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="156" priority="115" operator="equal">
+      <formula>"Mexicano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="155" priority="116" operator="equal">
+      <formula>"Para compartir"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="154" priority="117" operator="equal">
+      <formula>"Español"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="153" priority="118" operator="equal">
+      <formula>"Arroz"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="152" priority="119" operator="equal">
+      <formula>"Masa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="151" priority="120" operator="equal">
+      <formula>"Patata"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="150" priority="121" operator="equal">
+      <formula>"Comida rápida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="149" priority="122" operator="equal">
+      <formula>"Vegano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="148" priority="123" operator="equal">
+      <formula>"Peruano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="147" priority="124" operator="equal">
+      <formula>"Picante"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="146" priority="125" operator="equal">
+      <formula>"Frito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="145" priority="126" operator="equal">
+      <formula>"Marisco"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="144" priority="127" operator="equal">
+      <formula>"Vegetariano"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="143" priority="128" operator="equal">
+      <formula>"Japonés"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="142" priority="129" operator="equal">
+      <formula>"Desayuno"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="141" priority="130" operator="equal">
+      <formula>"Vegetales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="140" priority="131" operator="equal">
+      <formula>"Carne"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="139" priority="132" operator="equal">
+      <formula>"Frío"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="138" priority="133" operator="equal">
+      <formula>"Crudo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="137" priority="134" operator="equal">
+      <formula>"Sushi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="136" priority="135" operator="equal">
       <formula>"Pescado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3">
-    <cfRule type="cellIs" dxfId="811" priority="568" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="568" operator="equal">
       <formula>"Italiana"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="810" priority="569" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="569" operator="equal">
       <formula>"Francés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="809" priority="570" operator="equal">
+    <cfRule type="cellIs" dxfId="133" priority="570" operator="equal">
       <formula>"Pasta/Fideos"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="808" priority="571" operator="equal">
+    <cfRule type="cellIs" dxfId="132" priority="571" operator="equal">
       <formula>"Gourmet"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="807" priority="572" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="572" operator="equal">
       <formula>"Chino"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="806" priority="573" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="573" operator="equal">
       <formula>"Caldo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="805" priority="574" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="574" operator="equal">
       <formula>"Mexicano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="804" priority="575" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="575" operator="equal">
       <formula>"Para compartir"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="803" priority="576" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="576" operator="equal">
       <formula>"Español"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="802" priority="577" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="577" operator="equal">
       <formula>"Arroz"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="801" priority="578" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="578" operator="equal">
       <formula>"Masa"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="800" priority="579" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="579" operator="equal">
       <formula>"Patata"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="799" priority="580" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="580" operator="equal">
       <formula>"Comida rápida"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="798" priority="581" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="581" operator="equal">
       <formula>"Vegano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="797" priority="582" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="582" operator="equal">
       <formula>"Peruano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="796" priority="583" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="583" operator="equal">
       <formula>"Picante"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="795" priority="584" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="584" operator="equal">
       <formula>"Frito"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="794" priority="585" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="585" operator="equal">
       <formula>"Marisco"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="793" priority="586" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="586" operator="equal">
       <formula>"Vegetariano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="792" priority="587" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="587" operator="equal">
       <formula>"Japonés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="791" priority="588" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="588" operator="equal">
       <formula>"Desayuno"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="790" priority="589" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="589" operator="equal">
       <formula>"Vegetales"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="789" priority="590" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="590" operator="equal">
       <formula>"Carne"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="788" priority="591" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="591" operator="equal">
       <formula>"Frío"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="787" priority="592" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="592" operator="equal">
       <formula>"Crudo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="786" priority="593" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="593" operator="equal">
       <formula>"Sushi"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="785" priority="594" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="cellIs" dxfId="784" priority="541" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="783" priority="542" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="782" priority="543" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="781" priority="544" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="780" priority="545" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="779" priority="546" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="778" priority="547" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="777" priority="548" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="776" priority="549" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="775" priority="550" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="774" priority="551" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="773" priority="552" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="772" priority="553" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="771" priority="554" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="770" priority="555" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="769" priority="556" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="768" priority="557" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="767" priority="558" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="766" priority="559" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="765" priority="560" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="764" priority="561" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="763" priority="562" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="762" priority="563" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="761" priority="564" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="760" priority="565" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="759" priority="566" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="758" priority="567" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D6">
-    <cfRule type="cellIs" dxfId="757" priority="514" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="756" priority="515" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="755" priority="516" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="754" priority="517" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="753" priority="518" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="752" priority="519" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="751" priority="520" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="750" priority="521" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="749" priority="522" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="748" priority="523" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="747" priority="524" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="746" priority="525" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="745" priority="526" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="744" priority="527" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="743" priority="528" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="742" priority="529" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="741" priority="530" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="740" priority="531" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="739" priority="532" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="738" priority="533" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="737" priority="534" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="736" priority="535" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="735" priority="536" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="734" priority="537" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="733" priority="538" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="732" priority="539" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="731" priority="540" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6">
-    <cfRule type="cellIs" dxfId="730" priority="460" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="729" priority="461" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="728" priority="462" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="727" priority="463" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="726" priority="464" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="725" priority="465" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="724" priority="466" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="723" priority="467" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="722" priority="468" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="721" priority="469" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="720" priority="470" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="719" priority="471" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="718" priority="472" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="717" priority="473" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="716" priority="474" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="715" priority="475" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="714" priority="476" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="713" priority="477" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="712" priority="478" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="711" priority="479" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="710" priority="480" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="709" priority="481" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="708" priority="482" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="707" priority="483" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="706" priority="484" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="705" priority="485" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="704" priority="486" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J6">
-    <cfRule type="cellIs" dxfId="703" priority="433" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="702" priority="434" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="701" priority="435" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="700" priority="436" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="699" priority="437" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="698" priority="438" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="697" priority="439" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="696" priority="440" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="695" priority="441" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="694" priority="442" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="693" priority="443" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="692" priority="444" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="691" priority="445" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="690" priority="446" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="689" priority="447" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="688" priority="448" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="687" priority="449" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="686" priority="450" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="685" priority="451" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="684" priority="452" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="683" priority="453" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="682" priority="454" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="681" priority="455" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="680" priority="456" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="679" priority="457" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="678" priority="458" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="677" priority="459" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="594" operator="equal">
       <formula>"Pescado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6">
-    <cfRule type="cellIs" dxfId="676" priority="406" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="406" operator="equal">
       <formula>"Italiana"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="675" priority="407" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="407" operator="equal">
       <formula>"Francés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="674" priority="408" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="408" operator="equal">
       <formula>"Pasta/Fideos"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="673" priority="409" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="409" operator="equal">
       <formula>"Gourmet"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="672" priority="410" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="410" operator="equal">
       <formula>"Chino"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="671" priority="411" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="411" operator="equal">
       <formula>"Caldo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="670" priority="412" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="412" operator="equal">
       <formula>"Mexicano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="669" priority="413" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="413" operator="equal">
       <formula>"Para compartir"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="668" priority="414" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="414" operator="equal">
       <formula>"Español"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="667" priority="415" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="415" operator="equal">
       <formula>"Arroz"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="666" priority="416" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="416" operator="equal">
       <formula>"Masa"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="665" priority="417" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="417" operator="equal">
       <formula>"Patata"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="664" priority="418" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="418" operator="equal">
       <formula>"Comida rápida"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="663" priority="419" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="419" operator="equal">
       <formula>"Vegano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="662" priority="420" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="420" operator="equal">
       <formula>"Peruano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="661" priority="421" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="421" operator="equal">
       <formula>"Picante"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="660" priority="422" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="422" operator="equal">
       <formula>"Frito"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="659" priority="423" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="423" operator="equal">
       <formula>"Marisco"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="658" priority="424" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="424" operator="equal">
       <formula>"Vegetariano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="657" priority="425" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="425" operator="equal">
       <formula>"Japonés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="656" priority="426" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="426" operator="equal">
       <formula>"Desayuno"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="655" priority="427" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="427" operator="equal">
       <formula>"Vegetales"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="654" priority="428" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="428" operator="equal">
       <formula>"Carne"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="653" priority="429" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="429" operator="equal">
       <formula>"Frío"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="652" priority="430" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="430" operator="equal">
       <formula>"Crudo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="651" priority="431" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="431" operator="equal">
       <formula>"Sushi"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="650" priority="432" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9">
-    <cfRule type="cellIs" dxfId="649" priority="379" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="648" priority="380" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="647" priority="381" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="646" priority="382" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="645" priority="383" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="644" priority="384" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="643" priority="385" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="642" priority="386" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="641" priority="387" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="640" priority="388" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="639" priority="389" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="638" priority="390" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="637" priority="391" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="636" priority="392" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="635" priority="393" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="634" priority="394" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="633" priority="395" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="632" priority="396" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="631" priority="397" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="630" priority="398" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="629" priority="399" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="628" priority="400" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="627" priority="401" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="626" priority="402" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="625" priority="403" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="624" priority="404" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="623" priority="405" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9">
-    <cfRule type="cellIs" dxfId="622" priority="352" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="621" priority="353" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="620" priority="354" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="619" priority="355" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="618" priority="356" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="617" priority="357" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="616" priority="358" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="615" priority="359" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="614" priority="360" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="613" priority="361" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="612" priority="362" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="611" priority="363" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="610" priority="364" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="609" priority="365" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="608" priority="366" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="607" priority="367" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="606" priority="368" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="605" priority="369" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="604" priority="370" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="603" priority="371" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="602" priority="372" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="601" priority="373" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="600" priority="374" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="599" priority="375" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="598" priority="376" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="597" priority="377" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="596" priority="378" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" dxfId="595" priority="325" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="594" priority="326" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="593" priority="327" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="592" priority="328" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="591" priority="329" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="590" priority="330" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="589" priority="331" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="588" priority="332" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="587" priority="333" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="586" priority="334" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="585" priority="335" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="584" priority="336" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="583" priority="337" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="582" priority="338" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="581" priority="339" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="580" priority="340" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="579" priority="341" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="578" priority="342" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="577" priority="343" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="576" priority="344" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="575" priority="345" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="574" priority="346" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="573" priority="347" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="572" priority="348" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="571" priority="349" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="570" priority="350" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="569" priority="351" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H9">
-    <cfRule type="cellIs" dxfId="568" priority="298" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="567" priority="299" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="566" priority="300" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="565" priority="301" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="564" priority="302" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="563" priority="303" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="562" priority="304" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="561" priority="305" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="560" priority="306" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="559" priority="307" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="558" priority="308" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="557" priority="309" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="556" priority="310" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="555" priority="311" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="554" priority="312" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="553" priority="313" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="552" priority="314" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="551" priority="315" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="550" priority="316" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="549" priority="317" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="548" priority="318" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="547" priority="319" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="546" priority="320" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="545" priority="321" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="544" priority="322" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="543" priority="323" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="542" priority="324" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J9">
-    <cfRule type="cellIs" dxfId="541" priority="271" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="540" priority="272" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="539" priority="273" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="538" priority="274" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="537" priority="275" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="536" priority="276" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="535" priority="277" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="534" priority="278" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="533" priority="279" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="532" priority="280" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="531" priority="281" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="530" priority="282" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="529" priority="283" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="528" priority="284" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="527" priority="285" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="526" priority="286" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="525" priority="287" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="524" priority="288" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="523" priority="289" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="522" priority="290" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="521" priority="291" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="520" priority="292" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="519" priority="293" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="518" priority="294" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="517" priority="295" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="516" priority="296" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="515" priority="297" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="432" operator="equal">
       <formula>"Pescado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L9">
-    <cfRule type="cellIs" dxfId="514" priority="244" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="244" operator="equal">
       <formula>"Italiana"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="513" priority="245" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="245" operator="equal">
       <formula>"Francés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="512" priority="246" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="246" operator="equal">
       <formula>"Pasta/Fideos"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="511" priority="247" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="247" operator="equal">
       <formula>"Gourmet"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="510" priority="248" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="248" operator="equal">
       <formula>"Chino"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="509" priority="249" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="249" operator="equal">
       <formula>"Caldo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="508" priority="250" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="250" operator="equal">
       <formula>"Mexicano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="507" priority="251" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="251" operator="equal">
       <formula>"Para compartir"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="506" priority="252" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="252" operator="equal">
       <formula>"Español"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="505" priority="253" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="253" operator="equal">
       <formula>"Arroz"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="504" priority="254" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="254" operator="equal">
       <formula>"Masa"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="503" priority="255" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="255" operator="equal">
       <formula>"Patata"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="502" priority="256" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="256" operator="equal">
       <formula>"Comida rápida"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="501" priority="257" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="257" operator="equal">
       <formula>"Vegano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="500" priority="258" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="258" operator="equal">
       <formula>"Peruano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="499" priority="259" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="259" operator="equal">
       <formula>"Picante"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="498" priority="260" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="260" operator="equal">
       <formula>"Frito"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="497" priority="261" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="261" operator="equal">
       <formula>"Marisco"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="496" priority="262" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="262" operator="equal">
       <formula>"Vegetariano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="495" priority="263" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="263" operator="equal">
       <formula>"Japonés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="494" priority="264" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="264" operator="equal">
       <formula>"Desayuno"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="493" priority="265" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="265" operator="equal">
       <formula>"Vegetales"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="492" priority="266" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="266" operator="equal">
       <formula>"Carne"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="491" priority="267" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="267" operator="equal">
       <formula>"Frío"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="490" priority="268" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="268" operator="equal">
       <formula>"Crudo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="489" priority="269" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="269" operator="equal">
       <formula>"Sushi"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="488" priority="270" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="cellIs" dxfId="487" priority="217" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="486" priority="218" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="485" priority="219" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="484" priority="220" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="483" priority="221" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="482" priority="222" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="481" priority="223" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="480" priority="224" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="479" priority="225" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="478" priority="226" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="477" priority="227" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="476" priority="228" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="475" priority="229" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="474" priority="230" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="473" priority="231" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="472" priority="232" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="471" priority="233" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="470" priority="234" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="469" priority="235" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="468" priority="236" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="467" priority="237" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="466" priority="238" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="465" priority="239" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="464" priority="240" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="463" priority="241" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="462" priority="242" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="461" priority="243" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D12">
-    <cfRule type="cellIs" dxfId="460" priority="190" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="459" priority="191" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="458" priority="192" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="457" priority="193" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="456" priority="194" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="455" priority="195" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="454" priority="196" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="453" priority="197" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="452" priority="198" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="451" priority="199" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="450" priority="200" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="449" priority="201" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="448" priority="202" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="447" priority="203" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="446" priority="204" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="445" priority="205" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="444" priority="206" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="443" priority="207" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="442" priority="208" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="441" priority="209" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="440" priority="210" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="439" priority="211" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="438" priority="212" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="437" priority="213" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="436" priority="214" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="435" priority="215" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="434" priority="216" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="cellIs" dxfId="433" priority="163" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="432" priority="164" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="431" priority="165" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="430" priority="166" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="429" priority="167" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="428" priority="168" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="427" priority="169" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="426" priority="170" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="425" priority="171" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="424" priority="172" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="423" priority="173" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="422" priority="174" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="421" priority="175" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="420" priority="176" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="419" priority="177" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="418" priority="178" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="417" priority="179" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="416" priority="180" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="415" priority="181" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="414" priority="182" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="413" priority="183" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="412" priority="184" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="411" priority="185" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="410" priority="186" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="409" priority="187" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="408" priority="188" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="407" priority="189" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="cellIs" dxfId="406" priority="136" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="405" priority="137" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="404" priority="138" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="403" priority="139" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="402" priority="140" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="401" priority="141" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="400" priority="142" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="399" priority="143" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="398" priority="144" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="397" priority="145" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="396" priority="146" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="395" priority="147" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="394" priority="148" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="393" priority="149" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="392" priority="150" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="391" priority="151" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="390" priority="152" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="389" priority="153" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="388" priority="154" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="387" priority="155" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="386" priority="156" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="385" priority="157" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="384" priority="158" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="383" priority="159" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="382" priority="160" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="381" priority="161" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="380" priority="162" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J12">
-    <cfRule type="cellIs" dxfId="379" priority="109" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="378" priority="110" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="377" priority="111" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="376" priority="112" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="375" priority="113" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="374" priority="114" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="373" priority="115" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="372" priority="116" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="371" priority="117" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="370" priority="118" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="369" priority="119" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="368" priority="120" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="367" priority="121" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="366" priority="122" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="365" priority="123" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="364" priority="124" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="363" priority="125" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="362" priority="126" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="361" priority="127" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="360" priority="128" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="359" priority="129" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="358" priority="130" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="357" priority="131" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="356" priority="132" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="355" priority="133" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="354" priority="134" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="353" priority="135" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="270" operator="equal">
       <formula>"Pescado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L12">
-    <cfRule type="cellIs" dxfId="352" priority="82" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="82" operator="equal">
       <formula>"Italiana"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="351" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="83" operator="equal">
       <formula>"Francés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="350" priority="84" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="84" operator="equal">
       <formula>"Pasta/Fideos"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="349" priority="85" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="85" operator="equal">
       <formula>"Gourmet"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="348" priority="86" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="86" operator="equal">
       <formula>"Chino"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="347" priority="87" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="87" operator="equal">
       <formula>"Caldo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="346" priority="88" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="88" operator="equal">
       <formula>"Mexicano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="345" priority="89" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="89" operator="equal">
       <formula>"Para compartir"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="344" priority="90" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="90" operator="equal">
       <formula>"Español"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="343" priority="91" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="91" operator="equal">
       <formula>"Arroz"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="342" priority="92" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="92" operator="equal">
       <formula>"Masa"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="341" priority="93" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="93" operator="equal">
       <formula>"Patata"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="340" priority="94" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="94" operator="equal">
       <formula>"Comida rápida"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="339" priority="95" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="95" operator="equal">
       <formula>"Vegano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="338" priority="96" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="96" operator="equal">
       <formula>"Peruano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="337" priority="97" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="97" operator="equal">
       <formula>"Picante"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="336" priority="98" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="98" operator="equal">
       <formula>"Frito"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="335" priority="99" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="99" operator="equal">
       <formula>"Marisco"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="334" priority="100" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="100" operator="equal">
       <formula>"Vegetariano"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="333" priority="101" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="101" operator="equal">
       <formula>"Japonés"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="332" priority="102" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="102" operator="equal">
       <formula>"Desayuno"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="331" priority="103" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="103" operator="equal">
       <formula>"Vegetales"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="330" priority="104" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="104" operator="equal">
       <formula>"Carne"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="329" priority="105" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="105" operator="equal">
       <formula>"Frío"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="328" priority="106" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="106" operator="equal">
       <formula>"Crudo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="327" priority="107" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="107" operator="equal">
       <formula>"Sushi"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="326" priority="108" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B15">
-    <cfRule type="cellIs" dxfId="325" priority="55" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="324" priority="56" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="323" priority="57" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="322" priority="58" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="321" priority="59" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="320" priority="60" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="319" priority="61" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="318" priority="62" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="317" priority="63" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="316" priority="64" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="315" priority="65" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="314" priority="66" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="313" priority="67" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="312" priority="68" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="311" priority="69" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="310" priority="70" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="309" priority="71" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="308" priority="72" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="307" priority="73" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="306" priority="74" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="305" priority="75" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="304" priority="76" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="303" priority="77" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="302" priority="78" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="301" priority="79" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="300" priority="80" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="299" priority="81" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D15">
-    <cfRule type="cellIs" dxfId="298" priority="28" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="297" priority="29" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="296" priority="30" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="295" priority="31" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="294" priority="32" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="293" priority="33" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="292" priority="34" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="291" priority="35" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="290" priority="36" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="289" priority="37" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="288" priority="38" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="287" priority="39" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="286" priority="40" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="285" priority="41" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="284" priority="42" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="283" priority="43" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="282" priority="44" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="281" priority="45" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="280" priority="46" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="279" priority="47" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="278" priority="48" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="277" priority="49" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="276" priority="50" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="275" priority="51" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="274" priority="52" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="273" priority="53" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="272" priority="54" operator="equal">
-      <formula>"Pescado"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="cellIs" dxfId="271" priority="1" operator="equal">
-      <formula>"Italiana"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="270" priority="2" operator="equal">
-      <formula>"Francés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="269" priority="3" operator="equal">
-      <formula>"Pasta/Fideos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="268" priority="4" operator="equal">
-      <formula>"Gourmet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="267" priority="5" operator="equal">
-      <formula>"Chino"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="266" priority="6" operator="equal">
-      <formula>"Caldo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="265" priority="7" operator="equal">
-      <formula>"Mexicano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="264" priority="8" operator="equal">
-      <formula>"Para compartir"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="263" priority="9" operator="equal">
-      <formula>"Español"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="262" priority="10" operator="equal">
-      <formula>"Arroz"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="261" priority="11" operator="equal">
-      <formula>"Masa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="260" priority="12" operator="equal">
-      <formula>"Patata"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="259" priority="13" operator="equal">
-      <formula>"Comida rápida"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="258" priority="14" operator="equal">
-      <formula>"Vegano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="257" priority="15" operator="equal">
-      <formula>"Peruano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="256" priority="16" operator="equal">
-      <formula>"Picante"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="255" priority="17" operator="equal">
-      <formula>"Frito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="254" priority="18" operator="equal">
-      <formula>"Marisco"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="253" priority="19" operator="equal">
-      <formula>"Vegetariano"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="252" priority="20" operator="equal">
-      <formula>"Japonés"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="251" priority="21" operator="equal">
-      <formula>"Desayuno"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="250" priority="22" operator="equal">
-      <formula>"Vegetales"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="249" priority="23" operator="equal">
-      <formula>"Carne"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="248" priority="24" operator="equal">
-      <formula>"Frío"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="247" priority="25" operator="equal">
-      <formula>"Crudo"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="246" priority="26" operator="equal">
-      <formula>"Sushi"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="245" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="108" operator="equal">
       <formula>"Pescado"</formula>
     </cfRule>
   </conditionalFormatting>
